--- a/KK_Master_Target_List.xlsx
+++ b/KK_Master_Target_List.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,6 +38,12 @@
     <font>
       <name val="Calibri"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="000563C1"/>
+      <sz val="11"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="11">
@@ -119,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -132,6 +138,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -534,7 +543,7 @@
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
@@ -645,9 +654,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/edwardabood</t>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/edwardabood</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -662,7 +671,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr"/>
       <c r="K2" s="3" t="inlineStr"/>
-      <c r="L2" s="5" t="inlineStr">
+      <c r="L2" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -707,12 +716,12 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>NEEDS MANUAL FIND</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -720,7 +729,7 @@
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr"/>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="L3" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -765,12 +774,12 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>NEEDS MANUAL FIND</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -778,7 +787,7 @@
       <c r="I4" s="3" t="inlineStr"/>
       <c r="J4" s="3" t="inlineStr"/>
       <c r="K4" s="3" t="inlineStr"/>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="L4" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -823,9 +832,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/farhanfaruqui</t>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/farhanfaruqui</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -840,7 +849,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="L5" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -885,9 +894,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/lewisallsopp</t>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lewisallsopp</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -902,7 +911,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="3" t="inlineStr"/>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="L6" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -947,12 +956,12 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>NEEDS MANUAL FIND</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -960,7 +969,7 @@
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="L7" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1005,12 +1014,12 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>NEEDS MANUAL FIND</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1018,7 +1027,7 @@
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="3" t="inlineStr"/>
-      <c r="L8" s="5" t="inlineStr">
+      <c r="L8" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1063,9 +1072,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/andrewcummings-re</t>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/andrewcummings-re</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1080,7 +1089,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="5" t="inlineStr">
+      <c r="L9" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1125,9 +1134,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/stevenleckie-dubai</t>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/stevenleckie-dubai</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1142,7 +1151,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr"/>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="5" t="inlineStr">
+      <c r="L10" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1187,9 +1196,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/muhammadbinghatti</t>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/muhammadbinghatti</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1204,7 +1213,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="3" t="inlineStr"/>
-      <c r="L11" s="5" t="inlineStr">
+      <c r="L11" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1249,9 +1258,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/abdulkarimjaber</t>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/abdulkarimjaber</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1266,7 +1275,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr"/>
       <c r="K12" s="3" t="inlineStr"/>
-      <c r="L12" s="5" t="inlineStr">
+      <c r="L12" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1311,9 +1320,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/amirasajwani</t>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/amirasajwani</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1328,7 +1337,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr"/>
       <c r="K13" s="3" t="inlineStr"/>
-      <c r="L13" s="5" t="inlineStr">
+      <c r="L13" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1373,9 +1382,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/hussainsajwani</t>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hussainsajwani</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1390,7 +1399,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr"/>
       <c r="K14" s="3" t="inlineStr"/>
-      <c r="L14" s="5" t="inlineStr">
+      <c r="L14" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1435,9 +1444,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/ziadelchaar</t>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ziadelchaar</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1452,7 +1461,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr"/>
       <c r="K15" s="3" t="inlineStr"/>
-      <c r="L15" s="5" t="inlineStr">
+      <c r="L15" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1497,9 +1506,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/amitbhatt-danube</t>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/amitbhatt-danube</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1514,7 +1523,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr"/>
       <c r="K16" s="3" t="inlineStr"/>
-      <c r="L16" s="5" t="inlineStr">
+      <c r="L16" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1559,9 +1568,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/rizwansajan</t>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rizwansajan</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1576,7 +1585,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr"/>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="5" t="inlineStr">
+      <c r="L17" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1596,7 +1605,7 @@
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>NEEDS MANUAL FIND (founder/CEO)</t>
         </is>
@@ -1621,12 +1630,12 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G18" s="7" t="inlineStr">
         <is>
           <t>NEEDS MANUAL FIND</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1634,7 +1643,7 @@
       <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="3" t="inlineStr"/>
       <c r="K18" s="3" t="inlineStr"/>
-      <c r="L18" s="5" t="inlineStr">
+      <c r="L18" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1679,9 +1688,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/alonalurdes</t>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alonalurdes</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1696,7 +1705,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr"/>
       <c r="K19" s="3" t="inlineStr"/>
-      <c r="L19" s="5" t="inlineStr">
+      <c r="L19" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1716,7 +1725,7 @@
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>NEEDS MANUAL FIND (founder/CEO)</t>
         </is>
@@ -1741,12 +1750,12 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G20" s="7" t="inlineStr">
         <is>
           <t>NEEDS MANUAL FIND</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1754,7 +1763,7 @@
       <c r="I20" s="3" t="inlineStr"/>
       <c r="J20" s="3" t="inlineStr"/>
       <c r="K20" s="3" t="inlineStr"/>
-      <c r="L20" s="5" t="inlineStr">
+      <c r="L20" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1799,9 +1808,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/mohamedalabar</t>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mohamedalabar</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1816,7 +1825,7 @@
       </c>
       <c r="J21" s="3" t="inlineStr"/>
       <c r="K21" s="3" t="inlineStr"/>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="L21" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1861,12 +1870,12 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>NEEDS MANUAL FIND</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1874,7 +1883,7 @@
       <c r="I22" s="3" t="inlineStr"/>
       <c r="J22" s="3" t="inlineStr"/>
       <c r="K22" s="3" t="inlineStr"/>
-      <c r="L22" s="5" t="inlineStr">
+      <c r="L22" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1919,12 +1928,12 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>NEEDS MANUAL FIND</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1932,7 +1941,7 @@
       <c r="I23" s="3" t="inlineStr"/>
       <c r="J23" s="3" t="inlineStr"/>
       <c r="K23" s="3" t="inlineStr"/>
-      <c r="L23" s="5" t="inlineStr">
+      <c r="L23" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1977,9 +1986,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/firas-al-msaddi</t>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/firas-al-msaddi</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1994,7 +2003,7 @@
       </c>
       <c r="J24" s="3" t="inlineStr"/>
       <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="5" t="inlineStr">
+      <c r="L24" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2039,9 +2048,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/samirmokrani</t>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/samirmokrani</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2056,7 +2065,7 @@
       </c>
       <c r="J25" s="3" t="inlineStr"/>
       <c r="K25" s="3" t="inlineStr"/>
-      <c r="L25" s="5" t="inlineStr">
+      <c r="L25" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2101,9 +2110,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/svenolafahansen</t>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/svenolafahansen</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2118,7 +2127,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr"/>
       <c r="K26" s="3" t="inlineStr"/>
-      <c r="L26" s="5" t="inlineStr">
+      <c r="L26" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2138,7 +2147,7 @@
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>NEEDS MANUAL FIND (founder/CEO)</t>
         </is>
@@ -2163,12 +2172,12 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="G27" s="7" t="inlineStr">
         <is>
           <t>NEEDS MANUAL FIND</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2176,7 +2185,7 @@
       <c r="I27" s="3" t="inlineStr"/>
       <c r="J27" s="3" t="inlineStr"/>
       <c r="K27" s="3" t="inlineStr"/>
-      <c r="L27" s="5" t="inlineStr">
+      <c r="L27" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2221,9 +2230,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/nikitakuznetsov-mpp</t>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nikitakuznetsov-mpp</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2238,7 +2247,7 @@
       </c>
       <c r="J28" s="3" t="inlineStr"/>
       <c r="K28" s="3" t="inlineStr"/>
-      <c r="L28" s="5" t="inlineStr">
+      <c r="L28" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2283,9 +2292,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/patyamagomedova</t>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/patyamagomedova</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2300,7 +2309,7 @@
       </c>
       <c r="J29" s="3" t="inlineStr"/>
       <c r="K29" s="3" t="inlineStr"/>
-      <c r="L29" s="5" t="inlineStr">
+      <c r="L29" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2345,12 +2354,12 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="G30" s="7" t="inlineStr">
         <is>
           <t>NEEDS MANUAL FIND</t>
         </is>
       </c>
-      <c r="H30" s="7" t="inlineStr">
+      <c r="H30" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2358,7 +2367,7 @@
       <c r="I30" s="3" t="inlineStr"/>
       <c r="J30" s="3" t="inlineStr"/>
       <c r="K30" s="3" t="inlineStr"/>
-      <c r="L30" s="5" t="inlineStr">
+      <c r="L30" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2403,9 +2412,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/sudhirsyal</t>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sudhirsyal</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2420,7 +2429,7 @@
       </c>
       <c r="J31" s="3" t="inlineStr"/>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="5" t="inlineStr">
+      <c r="L31" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2465,12 +2474,12 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G32" s="6" t="inlineStr">
+      <c r="G32" s="7" t="inlineStr">
         <is>
           <t>NEEDS MANUAL FIND</t>
         </is>
       </c>
-      <c r="H32" s="7" t="inlineStr">
+      <c r="H32" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2478,7 +2487,7 @@
       <c r="I32" s="3" t="inlineStr"/>
       <c r="J32" s="3" t="inlineStr"/>
       <c r="K32" s="3" t="inlineStr"/>
-      <c r="L32" s="5" t="inlineStr">
+      <c r="L32" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2498,7 +2507,7 @@
       <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>NEEDS MANUAL FIND (founder/CEO)</t>
         </is>
@@ -2523,12 +2532,12 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G33" s="6" t="inlineStr">
+      <c r="G33" s="7" t="inlineStr">
         <is>
           <t>NEEDS MANUAL FIND</t>
         </is>
       </c>
-      <c r="H33" s="7" t="inlineStr">
+      <c r="H33" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2536,7 +2545,7 @@
       <c r="I33" s="3" t="inlineStr"/>
       <c r="J33" s="3" t="inlineStr"/>
       <c r="K33" s="3" t="inlineStr"/>
-      <c r="L33" s="5" t="inlineStr">
+      <c r="L33" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2581,12 +2590,12 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G34" s="6" t="inlineStr">
+      <c r="G34" s="7" t="inlineStr">
         <is>
           <t>NEEDS MANUAL FIND</t>
         </is>
       </c>
-      <c r="H34" s="7" t="inlineStr">
+      <c r="H34" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2594,7 +2603,7 @@
       <c r="I34" s="3" t="inlineStr"/>
       <c r="J34" s="3" t="inlineStr"/>
       <c r="K34" s="3" t="inlineStr"/>
-      <c r="L34" s="5" t="inlineStr">
+      <c r="L34" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2639,12 +2648,12 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G35" s="6" t="inlineStr">
+      <c r="G35" s="7" t="inlineStr">
         <is>
           <t>NEEDS MANUAL FIND</t>
         </is>
       </c>
-      <c r="H35" s="7" t="inlineStr">
+      <c r="H35" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2652,7 +2661,7 @@
       <c r="I35" s="3" t="inlineStr"/>
       <c r="J35" s="3" t="inlineStr"/>
       <c r="K35" s="3" t="inlineStr"/>
-      <c r="L35" s="5" t="inlineStr">
+      <c r="L35" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2697,12 +2706,12 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G36" s="6" t="inlineStr">
+      <c r="G36" s="7" t="inlineStr">
         <is>
           <t>NEEDS MANUAL FIND</t>
         </is>
       </c>
-      <c r="H36" s="7" t="inlineStr">
+      <c r="H36" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2710,7 +2719,7 @@
       <c r="I36" s="3" t="inlineStr"/>
       <c r="J36" s="3" t="inlineStr"/>
       <c r="K36" s="3" t="inlineStr"/>
-      <c r="L36" s="5" t="inlineStr">
+      <c r="L36" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2730,7 +2739,7 @@
       <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>NEEDS MANUAL FIND (founder/CEO)</t>
         </is>
@@ -2755,12 +2764,12 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G37" s="6" t="inlineStr">
+      <c r="G37" s="7" t="inlineStr">
         <is>
           <t>NEEDS MANUAL FIND</t>
         </is>
       </c>
-      <c r="H37" s="7" t="inlineStr">
+      <c r="H37" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2768,7 +2777,7 @@
       <c r="I37" s="3" t="inlineStr"/>
       <c r="J37" s="3" t="inlineStr"/>
       <c r="K37" s="3" t="inlineStr"/>
-      <c r="L37" s="5" t="inlineStr">
+      <c r="L37" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2813,9 +2822,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/arunnair-dubai</t>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/arunnair-dubai</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2830,7 +2839,7 @@
       </c>
       <c r="J38" s="3" t="inlineStr"/>
       <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="5" t="inlineStr">
+      <c r="L38" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2850,7 +2859,7 @@
       <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>NEEDS MANUAL FIND (founder/CEO)</t>
         </is>
@@ -2875,12 +2884,12 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G39" s="6" t="inlineStr">
+      <c r="G39" s="7" t="inlineStr">
         <is>
           <t>NEEDS MANUAL FIND</t>
         </is>
       </c>
-      <c r="H39" s="7" t="inlineStr">
+      <c r="H39" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2888,7 +2897,7 @@
       <c r="I39" s="3" t="inlineStr"/>
       <c r="J39" s="3" t="inlineStr"/>
       <c r="K39" s="3" t="inlineStr"/>
-      <c r="L39" s="5" t="inlineStr">
+      <c r="L39" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2933,9 +2942,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/pratappillai</t>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/pratappillai</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2950,7 +2959,7 @@
       </c>
       <c r="J40" s="3" t="inlineStr"/>
       <c r="K40" s="3" t="inlineStr"/>
-      <c r="L40" s="5" t="inlineStr">
+      <c r="L40" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2995,9 +3004,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/farrukhre</t>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/farrukhre</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3012,7 +3021,7 @@
       </c>
       <c r="J41" s="3" t="inlineStr"/>
       <c r="K41" s="3" t="inlineStr"/>
-      <c r="L41" s="5" t="inlineStr">
+      <c r="L41" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3032,7 +3041,7 @@
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>NEEDS MANUAL FIND (founder/CEO)</t>
         </is>
@@ -3057,12 +3066,12 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G42" s="6" t="inlineStr">
+      <c r="G42" s="7" t="inlineStr">
         <is>
           <t>NEEDS MANUAL FIND</t>
         </is>
       </c>
-      <c r="H42" s="7" t="inlineStr">
+      <c r="H42" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -3070,7 +3079,7 @@
       <c r="I42" s="3" t="inlineStr"/>
       <c r="J42" s="3" t="inlineStr"/>
       <c r="K42" s="3" t="inlineStr"/>
-      <c r="L42" s="5" t="inlineStr">
+      <c r="L42" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3115,9 +3124,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/niralishah-re</t>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/niralishah-re</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3132,7 +3141,7 @@
       </c>
       <c r="J43" s="3" t="inlineStr"/>
       <c r="K43" s="3" t="inlineStr"/>
-      <c r="L43" s="5" t="inlineStr">
+      <c r="L43" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3177,9 +3186,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/sanjayku</t>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sanjayku</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3194,7 +3203,7 @@
       </c>
       <c r="J44" s="3" t="inlineStr"/>
       <c r="K44" s="3" t="inlineStr"/>
-      <c r="L44" s="5" t="inlineStr">
+      <c r="L44" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3239,9 +3248,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/imranfarooq</t>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/imranfarooq</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3256,7 +3265,7 @@
       </c>
       <c r="J45" s="3" t="inlineStr"/>
       <c r="K45" s="3" t="inlineStr"/>
-      <c r="L45" s="5" t="inlineStr">
+      <c r="L45" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3301,12 +3310,12 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G46" s="6" t="inlineStr">
+      <c r="G46" s="7" t="inlineStr">
         <is>
           <t>NEEDS MANUAL FIND</t>
         </is>
       </c>
-      <c r="H46" s="7" t="inlineStr">
+      <c r="H46" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -3314,7 +3323,7 @@
       <c r="I46" s="3" t="inlineStr"/>
       <c r="J46" s="3" t="inlineStr"/>
       <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="5" t="inlineStr">
+      <c r="L46" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3359,9 +3368,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/farooqsyed</t>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/farooqsyed</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3376,7 +3385,7 @@
       </c>
       <c r="J47" s="3" t="inlineStr"/>
       <c r="K47" s="3" t="inlineStr"/>
-      <c r="L47" s="5" t="inlineStr">
+      <c r="L47" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3421,9 +3430,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G48" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/hussainalrahmoudi</t>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hussainalrahmoudi</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3438,7 +3447,7 @@
       </c>
       <c r="J48" s="3" t="inlineStr"/>
       <c r="K48" s="3" t="inlineStr"/>
-      <c r="L48" s="5" t="inlineStr">
+      <c r="L48" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3458,7 +3467,7 @@
       <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="6" t="inlineStr">
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>NEEDS MANUAL FIND (founder/CEO)</t>
         </is>
@@ -3483,12 +3492,12 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G49" s="6" t="inlineStr">
+      <c r="G49" s="7" t="inlineStr">
         <is>
           <t>NEEDS MANUAL FIND</t>
         </is>
       </c>
-      <c r="H49" s="7" t="inlineStr">
+      <c r="H49" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -3496,7 +3505,7 @@
       <c r="I49" s="3" t="inlineStr"/>
       <c r="J49" s="3" t="inlineStr"/>
       <c r="K49" s="3" t="inlineStr"/>
-      <c r="L49" s="5" t="inlineStr">
+      <c r="L49" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3541,9 +3550,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G50" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/zeinakhoury</t>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/zeinakhoury</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3558,7 +3567,7 @@
       </c>
       <c r="J50" s="3" t="inlineStr"/>
       <c r="K50" s="3" t="inlineStr"/>
-      <c r="L50" s="5" t="inlineStr">
+      <c r="L50" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3603,9 +3612,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/mohamedalhashimi</t>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mohamedalhashimi</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3620,7 +3629,7 @@
       </c>
       <c r="J51" s="3" t="inlineStr"/>
       <c r="K51" s="3" t="inlineStr"/>
-      <c r="L51" s="8" t="inlineStr">
+      <c r="L51" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3665,9 +3674,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G52" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/sultan-al-jaber</t>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sultan-al-jaber</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3682,7 +3691,7 @@
       </c>
       <c r="J52" s="3" t="inlineStr"/>
       <c r="K52" s="3" t="inlineStr"/>
-      <c r="L52" s="8" t="inlineStr">
+      <c r="L52" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3727,9 +3736,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G53" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/khalaf-al-habtoor</t>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/khalaf-al-habtoor</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3744,7 +3753,7 @@
       </c>
       <c r="J53" s="3" t="inlineStr"/>
       <c r="K53" s="3" t="inlineStr"/>
-      <c r="L53" s="8" t="inlineStr">
+      <c r="L53" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3764,7 +3773,7 @@
       <c r="A54" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="6" t="inlineStr">
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>NEEDS MANUAL FIND (founder/CEO)</t>
         </is>
@@ -3789,12 +3798,12 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G54" s="6" t="inlineStr">
+      <c r="G54" s="7" t="inlineStr">
         <is>
           <t>NEEDS MANUAL FIND</t>
         </is>
       </c>
-      <c r="H54" s="7" t="inlineStr">
+      <c r="H54" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -3802,7 +3811,7 @@
       <c r="I54" s="3" t="inlineStr"/>
       <c r="J54" s="3" t="inlineStr"/>
       <c r="K54" s="3" t="inlineStr"/>
-      <c r="L54" s="8" t="inlineStr">
+      <c r="L54" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3847,9 +3856,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G55" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/anasbukhash</t>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/anasbukhash</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3864,7 +3873,7 @@
       </c>
       <c r="J55" s="3" t="inlineStr"/>
       <c r="K55" s="3" t="inlineStr"/>
-      <c r="L55" s="8" t="inlineStr">
+      <c r="L55" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3909,9 +3918,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G56" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/binukunnumpurath</t>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/binukunnumpurath</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3926,7 +3935,7 @@
       </c>
       <c r="J56" s="3" t="inlineStr"/>
       <c r="K56" s="3" t="inlineStr"/>
-      <c r="L56" s="8" t="inlineStr">
+      <c r="L56" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3971,9 +3980,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/abdullaalhabai</t>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/abdullaalhabai</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3988,7 +3997,7 @@
       </c>
       <c r="J57" s="3" t="inlineStr"/>
       <c r="K57" s="3" t="inlineStr"/>
-      <c r="L57" s="8" t="inlineStr">
+      <c r="L57" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4033,9 +4042,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G58" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/faisalalbannai</t>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/faisalalbannai</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4050,7 +4059,7 @@
       </c>
       <c r="J58" s="3" t="inlineStr"/>
       <c r="K58" s="3" t="inlineStr"/>
-      <c r="L58" s="8" t="inlineStr">
+      <c r="L58" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4095,9 +4104,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G59" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/sunnyvarkey</t>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sunnyvarkey</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4112,7 +4121,7 @@
       </c>
       <c r="J59" s="3" t="inlineStr"/>
       <c r="K59" s="3" t="inlineStr"/>
-      <c r="L59" s="8" t="inlineStr">
+      <c r="L59" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4132,7 +4141,7 @@
       <c r="A60" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="B60" s="6" t="inlineStr">
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>NEEDS MANUAL FIND (founder/CEO)</t>
         </is>
@@ -4157,12 +4166,12 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G60" s="6" t="inlineStr">
+      <c r="G60" s="7" t="inlineStr">
         <is>
           <t>NEEDS MANUAL FIND</t>
         </is>
       </c>
-      <c r="H60" s="7" t="inlineStr">
+      <c r="H60" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -4170,7 +4179,7 @@
       <c r="I60" s="3" t="inlineStr"/>
       <c r="J60" s="3" t="inlineStr"/>
       <c r="K60" s="3" t="inlineStr"/>
-      <c r="L60" s="8" t="inlineStr">
+      <c r="L60" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4215,9 +4224,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/karimalsolh</t>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/karimalsolh</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4232,7 +4241,7 @@
       </c>
       <c r="J61" s="3" t="inlineStr"/>
       <c r="K61" s="3" t="inlineStr"/>
-      <c r="L61" s="8" t="inlineStr">
+      <c r="L61" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4277,9 +4286,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G62" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/raviraju-uae</t>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/raviraju-uae</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -4294,7 +4303,7 @@
       </c>
       <c r="J62" s="3" t="inlineStr"/>
       <c r="K62" s="3" t="inlineStr"/>
-      <c r="L62" s="8" t="inlineStr">
+      <c r="L62" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4339,9 +4348,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G63" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/jayesh-patel-re</t>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jayesh-patel-re</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -4356,7 +4365,7 @@
       </c>
       <c r="J63" s="3" t="inlineStr"/>
       <c r="K63" s="3" t="inlineStr"/>
-      <c r="L63" s="8" t="inlineStr">
+      <c r="L63" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4401,9 +4410,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G64" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/rashidghurair</t>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rashidghurair</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4418,7 +4427,7 @@
       </c>
       <c r="J64" s="3" t="inlineStr"/>
       <c r="K64" s="3" t="inlineStr"/>
-      <c r="L64" s="8" t="inlineStr">
+      <c r="L64" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4463,9 +4472,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G65" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/mohamedalzaabi</t>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mohamedalzaabi</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -4480,7 +4489,7 @@
       </c>
       <c r="J65" s="3" t="inlineStr"/>
       <c r="K65" s="3" t="inlineStr"/>
-      <c r="L65" s="8" t="inlineStr">
+      <c r="L65" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4525,12 +4534,12 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G66" s="6" t="inlineStr">
+      <c r="G66" s="7" t="inlineStr">
         <is>
           <t>NEEDS MANUAL FIND</t>
         </is>
       </c>
-      <c r="H66" s="7" t="inlineStr">
+      <c r="H66" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -4538,7 +4547,7 @@
       <c r="I66" s="3" t="inlineStr"/>
       <c r="J66" s="3" t="inlineStr"/>
       <c r="K66" s="3" t="inlineStr"/>
-      <c r="L66" s="8" t="inlineStr">
+      <c r="L66" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4558,7 +4567,7 @@
       <c r="A67" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="6" t="inlineStr">
+      <c r="B67" s="7" t="inlineStr">
         <is>
           <t>NEEDS MANUAL FIND (founder/CEO)</t>
         </is>
@@ -4583,12 +4592,12 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G67" s="6" t="inlineStr">
+      <c r="G67" s="7" t="inlineStr">
         <is>
           <t>NEEDS MANUAL FIND</t>
         </is>
       </c>
-      <c r="H67" s="7" t="inlineStr">
+      <c r="H67" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -4596,7 +4605,7 @@
       <c r="I67" s="3" t="inlineStr"/>
       <c r="J67" s="3" t="inlineStr"/>
       <c r="K67" s="3" t="inlineStr"/>
-      <c r="L67" s="8" t="inlineStr">
+      <c r="L67" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4641,9 +4650,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G68" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/sanjivsanghvi</t>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sanjivsanghvi</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4658,7 +4667,7 @@
       </c>
       <c r="J68" s="3" t="inlineStr"/>
       <c r="K68" s="3" t="inlineStr"/>
-      <c r="L68" s="8" t="inlineStr">
+      <c r="L68" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4703,9 +4712,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G69" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/pankaj-gupta-dubai</t>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/pankaj-gupta-dubai</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4720,7 +4729,7 @@
       </c>
       <c r="J69" s="3" t="inlineStr"/>
       <c r="K69" s="3" t="inlineStr"/>
-      <c r="L69" s="8" t="inlineStr">
+      <c r="L69" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4765,9 +4774,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G70" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/mehulkamdar</t>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mehulkamdar</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4782,7 +4791,7 @@
       </c>
       <c r="J70" s="3" t="inlineStr"/>
       <c r="K70" s="3" t="inlineStr"/>
-      <c r="L70" s="8" t="inlineStr">
+      <c r="L70" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4827,9 +4836,9 @@
           <t>UAE</t>
         </is>
       </c>
-      <c r="G71" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/saminaffakh</t>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/saminaffakh</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4844,7 +4853,7 @@
       </c>
       <c r="J71" s="3" t="inlineStr"/>
       <c r="K71" s="3" t="inlineStr"/>
-      <c r="L71" s="9" t="inlineStr">
+      <c r="L71" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -4889,9 +4898,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G72" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/genevieveleveille</t>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/genevieveleveille</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4906,7 +4915,7 @@
       </c>
       <c r="J72" s="3" t="inlineStr"/>
       <c r="K72" s="3" t="inlineStr"/>
-      <c r="L72" s="8" t="inlineStr">
+      <c r="L72" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4951,9 +4960,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G73" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/robsherwood</t>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/robsherwood</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4968,7 +4977,7 @@
       </c>
       <c r="J73" s="3" t="inlineStr"/>
       <c r="K73" s="3" t="inlineStr"/>
-      <c r="L73" s="8" t="inlineStr">
+      <c r="L73" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5013,9 +5022,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G74" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/matthew-biddle</t>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/matthew-biddle</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5030,7 +5039,7 @@
       </c>
       <c r="J74" s="3" t="inlineStr"/>
       <c r="K74" s="3" t="inlineStr"/>
-      <c r="L74" s="8" t="inlineStr">
+      <c r="L74" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5075,9 +5084,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G75" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/camilla-dell</t>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/camilla-dell</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5092,7 +5101,7 @@
       </c>
       <c r="J75" s="3" t="inlineStr"/>
       <c r="K75" s="3" t="inlineStr"/>
-      <c r="L75" s="8" t="inlineStr">
+      <c r="L75" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5137,9 +5146,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G76" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/simon-carter-bl</t>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/simon-carter-bl</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -5154,7 +5163,7 @@
       </c>
       <c r="J76" s="3" t="inlineStr"/>
       <c r="K76" s="3" t="inlineStr"/>
-      <c r="L76" s="8" t="inlineStr">
+      <c r="L76" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5199,9 +5208,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G77" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/nickcandy</t>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nickcandy</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -5216,7 +5225,7 @@
       </c>
       <c r="J77" s="3" t="inlineStr"/>
       <c r="K77" s="3" t="inlineStr"/>
-      <c r="L77" s="8" t="inlineStr">
+      <c r="L77" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5261,9 +5270,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G78" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/johnnycaudwell</t>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/johnnycaudwell</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -5278,7 +5287,7 @@
       </c>
       <c r="J78" s="3" t="inlineStr"/>
       <c r="K78" s="3" t="inlineStr"/>
-      <c r="L78" s="8" t="inlineStr">
+      <c r="L78" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5323,9 +5332,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G79" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/emily-wright-proptech</t>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/emily-wright-proptech</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -5340,7 +5349,7 @@
       </c>
       <c r="J79" s="3" t="inlineStr"/>
       <c r="K79" s="3" t="inlineStr"/>
-      <c r="L79" s="8" t="inlineStr">
+      <c r="L79" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5385,9 +5394,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G80" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/adamday-easyproperty</t>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/adamday-easyproperty</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -5402,7 +5411,7 @@
       </c>
       <c r="J80" s="3" t="inlineStr"/>
       <c r="K80" s="3" t="inlineStr"/>
-      <c r="L80" s="8" t="inlineStr">
+      <c r="L80" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5447,9 +5456,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G81" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/guygittins</t>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/guygittins</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -5464,7 +5473,7 @@
       </c>
       <c r="J81" s="3" t="inlineStr"/>
       <c r="K81" s="3" t="inlineStr"/>
-      <c r="L81" s="8" t="inlineStr">
+      <c r="L81" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5509,9 +5518,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G82" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/galliard-homes</t>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/galliard-homes</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -5526,7 +5535,7 @@
       </c>
       <c r="J82" s="3" t="inlineStr"/>
       <c r="K82" s="3" t="inlineStr"/>
-      <c r="L82" s="8" t="inlineStr">
+      <c r="L82" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5571,9 +5580,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G83" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/patrickmcgrath</t>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/patrickmcgrath</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -5588,7 +5597,7 @@
       </c>
       <c r="J83" s="3" t="inlineStr"/>
       <c r="K83" s="3" t="inlineStr"/>
-      <c r="L83" s="8" t="inlineStr">
+      <c r="L83" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5633,9 +5642,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G84" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/rorymcmullan</t>
+      <c r="G84" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rorymcmullan</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -5650,7 +5659,7 @@
       </c>
       <c r="J84" s="3" t="inlineStr"/>
       <c r="K84" s="3" t="inlineStr"/>
-      <c r="L84" s="8" t="inlineStr">
+      <c r="L84" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5695,9 +5704,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G85" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/timmencer</t>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/timmencer</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -5712,7 +5721,7 @@
       </c>
       <c r="J85" s="3" t="inlineStr"/>
       <c r="K85" s="3" t="inlineStr"/>
-      <c r="L85" s="8" t="inlineStr">
+      <c r="L85" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5757,9 +5766,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G86" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/sophie-gosling-hs</t>
+      <c r="G86" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sophie-gosling-hs</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5774,7 +5783,7 @@
       </c>
       <c r="J86" s="3" t="inlineStr"/>
       <c r="K86" s="3" t="inlineStr"/>
-      <c r="L86" s="8" t="inlineStr">
+      <c r="L86" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5819,9 +5828,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G87" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/henrypryor</t>
+      <c r="G87" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/henrypryor</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5836,7 +5845,7 @@
       </c>
       <c r="J87" s="3" t="inlineStr"/>
       <c r="K87" s="3" t="inlineStr"/>
-      <c r="L87" s="8" t="inlineStr">
+      <c r="L87" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5881,9 +5890,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G88" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/naomi-heaton</t>
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/naomi-heaton</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5898,7 +5907,7 @@
       </c>
       <c r="J88" s="3" t="inlineStr"/>
       <c r="K88" s="3" t="inlineStr"/>
-      <c r="L88" s="8" t="inlineStr">
+      <c r="L88" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5943,9 +5952,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G89" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/andrewjones-lmp</t>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/andrewjones-lmp</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5960,7 +5969,7 @@
       </c>
       <c r="J89" s="3" t="inlineStr"/>
       <c r="K89" s="3" t="inlineStr"/>
-      <c r="L89" s="8" t="inlineStr">
+      <c r="L89" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6005,9 +6014,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G90" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/asifmerchant</t>
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/asifmerchant</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -6022,7 +6031,7 @@
       </c>
       <c r="J90" s="3" t="inlineStr"/>
       <c r="K90" s="3" t="inlineStr"/>
-      <c r="L90" s="8" t="inlineStr">
+      <c r="L90" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6067,9 +6076,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G91" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/markhaywardnaea</t>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/markhaywardnaea</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -6084,7 +6093,7 @@
       </c>
       <c r="J91" s="3" t="inlineStr"/>
       <c r="K91" s="3" t="inlineStr"/>
-      <c r="L91" s="8" t="inlineStr">
+      <c r="L91" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6129,9 +6138,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G92" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/matthewfarrell-pm</t>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/matthewfarrell-pm</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -6146,7 +6155,7 @@
       </c>
       <c r="J92" s="3" t="inlineStr"/>
       <c r="K92" s="3" t="inlineStr"/>
-      <c r="L92" s="8" t="inlineStr">
+      <c r="L92" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6191,9 +6200,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G93" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/robhoughton</t>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/robhoughton</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -6208,7 +6217,7 @@
       </c>
       <c r="J93" s="3" t="inlineStr"/>
       <c r="K93" s="3" t="inlineStr"/>
-      <c r="L93" s="8" t="inlineStr">
+      <c r="L93" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6253,9 +6262,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G94" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/johansvanstrom</t>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/johansvanstrom</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -6270,7 +6279,7 @@
       </c>
       <c r="J94" s="3" t="inlineStr"/>
       <c r="K94" s="3" t="inlineStr"/>
-      <c r="L94" s="8" t="inlineStr">
+      <c r="L94" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6315,9 +6324,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G95" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/kate-orwin</t>
+      <c r="G95" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kate-orwin</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -6332,7 +6341,7 @@
       </c>
       <c r="J95" s="3" t="inlineStr"/>
       <c r="K95" s="3" t="inlineStr"/>
-      <c r="L95" s="8" t="inlineStr">
+      <c r="L95" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6377,9 +6386,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G96" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/tariqiqureishy</t>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tariqiqureishy</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -6394,7 +6403,7 @@
       </c>
       <c r="J96" s="3" t="inlineStr"/>
       <c r="K96" s="3" t="inlineStr"/>
-      <c r="L96" s="8" t="inlineStr">
+      <c r="L96" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6439,9 +6448,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G97" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/jamesdearsley</t>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jamesdearsley</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -6456,7 +6465,7 @@
       </c>
       <c r="J97" s="3" t="inlineStr"/>
       <c r="K97" s="3" t="inlineStr"/>
-      <c r="L97" s="8" t="inlineStr">
+      <c r="L97" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6501,9 +6510,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G98" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/rorypenn</t>
+      <c r="G98" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rorypenn</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -6518,7 +6527,7 @@
       </c>
       <c r="J98" s="3" t="inlineStr"/>
       <c r="K98" s="3" t="inlineStr"/>
-      <c r="L98" s="8" t="inlineStr">
+      <c r="L98" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6563,9 +6572,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G99" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/daniel-attia</t>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/daniel-attia</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -6580,7 +6589,7 @@
       </c>
       <c r="J99" s="3" t="inlineStr"/>
       <c r="K99" s="3" t="inlineStr"/>
-      <c r="L99" s="8" t="inlineStr">
+      <c r="L99" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6625,9 +6634,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G100" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/kunlecampbell</t>
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kunlecampbell</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -6642,7 +6651,7 @@
       </c>
       <c r="J100" s="3" t="inlineStr"/>
       <c r="K100" s="3" t="inlineStr"/>
-      <c r="L100" s="9" t="inlineStr">
+      <c r="L100" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -6687,9 +6696,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G101" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/aliabdaal</t>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/aliabdaal</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -6704,7 +6713,7 @@
       </c>
       <c r="J101" s="3" t="inlineStr"/>
       <c r="K101" s="3" t="inlineStr"/>
-      <c r="L101" s="9" t="inlineStr">
+      <c r="L101" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -6749,9 +6758,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G102" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/helentupper</t>
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/helentupper</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -6766,7 +6775,7 @@
       </c>
       <c r="J102" s="3" t="inlineStr"/>
       <c r="K102" s="3" t="inlineStr"/>
-      <c r="L102" s="9" t="inlineStr">
+      <c r="L102" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -6811,9 +6820,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G103" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/jamesanderson-re</t>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jamesanderson-re</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -6828,7 +6837,7 @@
       </c>
       <c r="J103" s="3" t="inlineStr"/>
       <c r="K103" s="3" t="inlineStr"/>
-      <c r="L103" s="9" t="inlineStr">
+      <c r="L103" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -6873,9 +6882,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G104" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/martingilbert</t>
+      <c r="G104" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/martingilbert</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -6890,7 +6899,7 @@
       </c>
       <c r="J104" s="3" t="inlineStr"/>
       <c r="K104" s="3" t="inlineStr"/>
-      <c r="L104" s="9" t="inlineStr">
+      <c r="L104" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -6935,9 +6944,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G105" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/merryn-somerset-webb</t>
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/merryn-somerset-webb</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -6952,7 +6961,7 @@
       </c>
       <c r="J105" s="3" t="inlineStr"/>
       <c r="K105" s="3" t="inlineStr"/>
-      <c r="L105" s="9" t="inlineStr">
+      <c r="L105" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -6997,9 +7006,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G106" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/jameswatt</t>
+      <c r="G106" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jameswatt</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -7014,7 +7023,7 @@
       </c>
       <c r="J106" s="3" t="inlineStr"/>
       <c r="K106" s="3" t="inlineStr"/>
-      <c r="L106" s="9" t="inlineStr">
+      <c r="L106" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -7059,9 +7068,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G107" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/scottmacdonald-fm</t>
+      <c r="G107" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/scottmacdonald-fm</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -7076,7 +7085,7 @@
       </c>
       <c r="J107" s="3" t="inlineStr"/>
       <c r="K107" s="3" t="inlineStr"/>
-      <c r="L107" s="9" t="inlineStr">
+      <c r="L107" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -7121,9 +7130,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G108" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/tarabutton</t>
+      <c r="G108" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tarabutton</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -7138,7 +7147,7 @@
       </c>
       <c r="J108" s="3" t="inlineStr"/>
       <c r="K108" s="3" t="inlineStr"/>
-      <c r="L108" s="9" t="inlineStr">
+      <c r="L108" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -7183,9 +7192,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G109" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/alexhardee</t>
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alexhardee</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -7200,7 +7209,7 @@
       </c>
       <c r="J109" s="3" t="inlineStr"/>
       <c r="K109" s="3" t="inlineStr"/>
-      <c r="L109" s="9" t="inlineStr">
+      <c r="L109" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -7245,9 +7254,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G110" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/emmabanks</t>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/emmabanks</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -7262,7 +7271,7 @@
       </c>
       <c r="J110" s="3" t="inlineStr"/>
       <c r="K110" s="3" t="inlineStr"/>
-      <c r="L110" s="9" t="inlineStr">
+      <c r="L110" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -7307,9 +7316,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G111" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/rogerbootle</t>
+      <c r="G111" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rogerbootle</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -7324,7 +7333,7 @@
       </c>
       <c r="J111" s="3" t="inlineStr"/>
       <c r="K111" s="3" t="inlineStr"/>
-      <c r="L111" s="9" t="inlineStr">
+      <c r="L111" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -7369,9 +7378,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G112" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/priyalakhani</t>
+      <c r="G112" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/priyalakhani</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -7386,7 +7395,7 @@
       </c>
       <c r="J112" s="3" t="inlineStr"/>
       <c r="K112" s="3" t="inlineStr"/>
-      <c r="L112" s="9" t="inlineStr">
+      <c r="L112" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -7431,9 +7440,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G113" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/sanjeevbahl</t>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sanjeevbahl</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -7448,7 +7457,7 @@
       </c>
       <c r="J113" s="3" t="inlineStr"/>
       <c r="K113" s="3" t="inlineStr"/>
-      <c r="L113" s="9" t="inlineStr">
+      <c r="L113" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -7493,9 +7502,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G114" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/karanbilimoria</t>
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/karanbilimoria</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -7510,7 +7519,7 @@
       </c>
       <c r="J114" s="3" t="inlineStr"/>
       <c r="K114" s="3" t="inlineStr"/>
-      <c r="L114" s="9" t="inlineStr">
+      <c r="L114" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -7555,9 +7564,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G115" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/aimeenoel</t>
+      <c r="G115" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/aimeenoel</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -7572,7 +7581,7 @@
       </c>
       <c r="J115" s="3" t="inlineStr"/>
       <c r="K115" s="3" t="inlineStr"/>
-      <c r="L115" s="9" t="inlineStr">
+      <c r="L115" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -7617,9 +7626,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G116" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/chloethomas</t>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/chloethomas</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -7634,7 +7643,7 @@
       </c>
       <c r="J116" s="3" t="inlineStr"/>
       <c r="K116" s="3" t="inlineStr"/>
-      <c r="L116" s="9" t="inlineStr">
+      <c r="L116" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -7679,9 +7688,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G117" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/mohsinissa</t>
+      <c r="G117" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mohsinissa</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -7696,7 +7705,7 @@
       </c>
       <c r="J117" s="3" t="inlineStr"/>
       <c r="K117" s="3" t="inlineStr"/>
-      <c r="L117" s="9" t="inlineStr">
+      <c r="L117" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -7741,9 +7750,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G118" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/azhar</t>
+      <c r="G118" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/azhar</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -7758,7 +7767,7 @@
       </c>
       <c r="J118" s="3" t="inlineStr"/>
       <c r="K118" s="3" t="inlineStr"/>
-      <c r="L118" s="9" t="inlineStr">
+      <c r="L118" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -7803,9 +7812,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G119" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/sheilaflavell</t>
+      <c r="G119" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sheilaflavell</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -7820,7 +7829,7 @@
       </c>
       <c r="J119" s="3" t="inlineStr"/>
       <c r="K119" s="3" t="inlineStr"/>
-      <c r="L119" s="9" t="inlineStr">
+      <c r="L119" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -7865,9 +7874,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G120" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/annerichards</t>
+      <c r="G120" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/annerichards</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -7882,7 +7891,7 @@
       </c>
       <c r="J120" s="3" t="inlineStr"/>
       <c r="K120" s="3" t="inlineStr"/>
-      <c r="L120" s="9" t="inlineStr">
+      <c r="L120" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -7927,9 +7936,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G121" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/christianafigueres</t>
+      <c r="G121" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/christianafigueres</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -7944,7 +7953,7 @@
       </c>
       <c r="J121" s="3" t="inlineStr"/>
       <c r="K121" s="3" t="inlineStr"/>
-      <c r="L121" s="9" t="inlineStr">
+      <c r="L121" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -7989,9 +7998,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G122" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/joconfino</t>
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/joconfino</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -8006,7 +8015,7 @@
       </c>
       <c r="J122" s="3" t="inlineStr"/>
       <c r="K122" s="3" t="inlineStr"/>
-      <c r="L122" s="9" t="inlineStr">
+      <c r="L122" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -8051,9 +8060,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G123" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/benhammersley</t>
+      <c r="G123" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/benhammersley</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -8068,7 +8077,7 @@
       </c>
       <c r="J123" s="3" t="inlineStr"/>
       <c r="K123" s="3" t="inlineStr"/>
-      <c r="L123" s="9" t="inlineStr">
+      <c r="L123" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -8113,9 +8122,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G124" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/harveygoldsmith</t>
+      <c r="G124" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/harveygoldsmith</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -8130,7 +8139,7 @@
       </c>
       <c r="J124" s="3" t="inlineStr"/>
       <c r="K124" s="3" t="inlineStr"/>
-      <c r="L124" s="9" t="inlineStr">
+      <c r="L124" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -8175,9 +8184,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G125" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/jeremywaite</t>
+      <c r="G125" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jeremywaite</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -8192,7 +8201,7 @@
       </c>
       <c r="J125" s="3" t="inlineStr"/>
       <c r="K125" s="3" t="inlineStr"/>
-      <c r="L125" s="9" t="inlineStr">
+      <c r="L125" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -8237,9 +8246,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G126" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/timskeet</t>
+      <c r="G126" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/timskeet</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -8254,7 +8263,7 @@
       </c>
       <c r="J126" s="3" t="inlineStr"/>
       <c r="K126" s="3" t="inlineStr"/>
-      <c r="L126" s="9" t="inlineStr">
+      <c r="L126" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -8299,9 +8308,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G127" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/timkilroy</t>
+      <c r="G127" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/timkilroy</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -8316,7 +8325,7 @@
       </c>
       <c r="J127" s="3" t="inlineStr"/>
       <c r="K127" s="3" t="inlineStr"/>
-      <c r="L127" s="9" t="inlineStr">
+      <c r="L127" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -8361,9 +8370,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G128" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/jade-tambini</t>
+      <c r="G128" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jade-tambini</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -8378,7 +8387,7 @@
       </c>
       <c r="J128" s="3" t="inlineStr"/>
       <c r="K128" s="3" t="inlineStr"/>
-      <c r="L128" s="9" t="inlineStr">
+      <c r="L128" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -8423,9 +8432,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G129" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/khalidmostefaoui</t>
+      <c r="G129" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/khalidmostefaoui</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -8440,7 +8449,7 @@
       </c>
       <c r="J129" s="3" t="inlineStr"/>
       <c r="K129" s="3" t="inlineStr"/>
-      <c r="L129" s="9" t="inlineStr">
+      <c r="L129" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -8485,9 +8494,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G130" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/johngoodall</t>
+      <c r="G130" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/johngoodall</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -8502,7 +8511,7 @@
       </c>
       <c r="J130" s="3" t="inlineStr"/>
       <c r="K130" s="3" t="inlineStr"/>
-      <c r="L130" s="9" t="inlineStr">
+      <c r="L130" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -8547,9 +8556,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G131" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/marcus-cauchi</t>
+      <c r="G131" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/marcus-cauchi</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -8564,7 +8573,7 @@
       </c>
       <c r="J131" s="3" t="inlineStr"/>
       <c r="K131" s="3" t="inlineStr"/>
-      <c r="L131" s="9" t="inlineStr">
+      <c r="L131" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -8609,9 +8618,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G132" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/nickferrari</t>
+      <c r="G132" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nickferrari</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -8626,7 +8635,7 @@
       </c>
       <c r="J132" s="3" t="inlineStr"/>
       <c r="K132" s="3" t="inlineStr"/>
-      <c r="L132" s="9" t="inlineStr">
+      <c r="L132" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -8671,9 +8680,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G133" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/ewenmackinnon</t>
+      <c r="G133" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ewenmackinnon</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -8688,7 +8697,7 @@
       </c>
       <c r="J133" s="3" t="inlineStr"/>
       <c r="K133" s="3" t="inlineStr"/>
-      <c r="L133" s="9" t="inlineStr">
+      <c r="L133" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -8733,9 +8742,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G134" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/lilachbullock</t>
+      <c r="G134" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lilachbullock</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -8750,7 +8759,7 @@
       </c>
       <c r="J134" s="3" t="inlineStr"/>
       <c r="K134" s="3" t="inlineStr"/>
-      <c r="L134" s="9" t="inlineStr">
+      <c r="L134" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -8795,9 +8804,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G135" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/lukecarthy</t>
+      <c r="G135" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lukecarthy</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -8812,7 +8821,7 @@
       </c>
       <c r="J135" s="3" t="inlineStr"/>
       <c r="K135" s="3" t="inlineStr"/>
-      <c r="L135" s="9" t="inlineStr">
+      <c r="L135" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -8857,9 +8866,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G136" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/tomaschamorro</t>
+      <c r="G136" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tomaschamorro</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -8874,7 +8883,7 @@
       </c>
       <c r="J136" s="3" t="inlineStr"/>
       <c r="K136" s="3" t="inlineStr"/>
-      <c r="L136" s="9" t="inlineStr">
+      <c r="L136" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -8919,9 +8928,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G137" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/chriscarey-music</t>
+      <c r="G137" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/chriscarey-music</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -8936,7 +8945,7 @@
       </c>
       <c r="J137" s="3" t="inlineStr"/>
       <c r="K137" s="3" t="inlineStr"/>
-      <c r="L137" s="9" t="inlineStr">
+      <c r="L137" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -8981,9 +8990,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G138" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/shafi-ahmed</t>
+      <c r="G138" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/shafi-ahmed</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -8998,7 +9007,7 @@
       </c>
       <c r="J138" s="3" t="inlineStr"/>
       <c r="K138" s="3" t="inlineStr"/>
-      <c r="L138" s="9" t="inlineStr">
+      <c r="L138" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -9043,9 +9052,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G139" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/russtannen</t>
+      <c r="G139" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/russtannen</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -9060,7 +9069,7 @@
       </c>
       <c r="J139" s="3" t="inlineStr"/>
       <c r="K139" s="3" t="inlineStr"/>
-      <c r="L139" s="9" t="inlineStr">
+      <c r="L139" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -9105,9 +9114,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G140" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/mustafa-suleyman</t>
+      <c r="G140" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mustafa-suleyman</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -9122,7 +9131,7 @@
       </c>
       <c r="J140" s="3" t="inlineStr"/>
       <c r="K140" s="3" t="inlineStr"/>
-      <c r="L140" s="9" t="inlineStr">
+      <c r="L140" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -9167,9 +9176,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G141" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/tobymildon</t>
+      <c r="G141" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tobymildon</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -9184,7 +9193,7 @@
       </c>
       <c r="J141" s="3" t="inlineStr"/>
       <c r="K141" s="3" t="inlineStr"/>
-      <c r="L141" s="9" t="inlineStr">
+      <c r="L141" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -9229,9 +9238,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G142" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/emmavigus</t>
+      <c r="G142" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/emmavigus</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -9246,7 +9255,7 @@
       </c>
       <c r="J142" s="3" t="inlineStr"/>
       <c r="K142" s="3" t="inlineStr"/>
-      <c r="L142" s="9" t="inlineStr">
+      <c r="L142" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -9291,9 +9300,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G143" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/tylerbrule</t>
+      <c r="G143" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tylerbrule</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -9308,7 +9317,7 @@
       </c>
       <c r="J143" s="3" t="inlineStr"/>
       <c r="K143" s="3" t="inlineStr"/>
-      <c r="L143" s="9" t="inlineStr">
+      <c r="L143" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -9353,9 +9362,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G144" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/jbradford</t>
+      <c r="G144" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jbradford</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -9370,7 +9379,7 @@
       </c>
       <c r="J144" s="3" t="inlineStr"/>
       <c r="K144" s="3" t="inlineStr"/>
-      <c r="L144" s="9" t="inlineStr">
+      <c r="L144" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -9415,9 +9424,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G145" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/jonollier</t>
+      <c r="G145" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jonollier</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -9432,7 +9441,7 @@
       </c>
       <c r="J145" s="3" t="inlineStr"/>
       <c r="K145" s="3" t="inlineStr"/>
-      <c r="L145" s="9" t="inlineStr">
+      <c r="L145" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -9477,9 +9486,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G146" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/sharonosbourne</t>
+      <c r="G146" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sharonosbourne</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -9494,7 +9503,7 @@
       </c>
       <c r="J146" s="3" t="inlineStr"/>
       <c r="K146" s="3" t="inlineStr"/>
-      <c r="L146" s="9" t="inlineStr">
+      <c r="L146" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -9539,9 +9548,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G147" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/kirstymacdonaldfinance</t>
+      <c r="G147" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kirstymacdonaldfinance</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -9556,7 +9565,7 @@
       </c>
       <c r="J147" s="3" t="inlineStr"/>
       <c r="K147" s="3" t="inlineStr"/>
-      <c r="L147" s="9" t="inlineStr">
+      <c r="L147" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -9601,9 +9610,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G148" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/laramorgan</t>
+      <c r="G148" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/laramorgan</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -9618,7 +9627,7 @@
       </c>
       <c r="J148" s="3" t="inlineStr"/>
       <c r="K148" s="3" t="inlineStr"/>
-      <c r="L148" s="9" t="inlineStr">
+      <c r="L148" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -9663,9 +9672,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G149" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/amandastveley</t>
+      <c r="G149" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/amandastveley</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -9680,7 +9689,7 @@
       </c>
       <c r="J149" s="3" t="inlineStr"/>
       <c r="K149" s="3" t="inlineStr"/>
-      <c r="L149" s="9" t="inlineStr">
+      <c r="L149" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -9725,9 +9734,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G150" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/poonamgupta-re</t>
+      <c r="G150" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/poonamgupta-re</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -9742,7 +9751,7 @@
       </c>
       <c r="J150" s="3" t="inlineStr"/>
       <c r="K150" s="3" t="inlineStr"/>
-      <c r="L150" s="9" t="inlineStr">
+      <c r="L150" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -9787,9 +9796,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G151" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/davehazlehurst</t>
+      <c r="G151" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/davehazlehurst</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -9804,7 +9813,7 @@
       </c>
       <c r="J151" s="3" t="inlineStr"/>
       <c r="K151" s="3" t="inlineStr"/>
-      <c r="L151" s="9" t="inlineStr">
+      <c r="L151" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -9849,9 +9858,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G152" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/nareshwaney</t>
+      <c r="G152" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nareshwaney</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -9866,7 +9875,7 @@
       </c>
       <c r="J152" s="3" t="inlineStr"/>
       <c r="K152" s="3" t="inlineStr"/>
-      <c r="L152" s="9" t="inlineStr">
+      <c r="L152" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -9911,9 +9920,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G153" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/hungle</t>
+      <c r="G153" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hungle</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -9928,7 +9937,7 @@
       </c>
       <c r="J153" s="3" t="inlineStr"/>
       <c r="K153" s="3" t="inlineStr"/>
-      <c r="L153" s="9" t="inlineStr">
+      <c r="L153" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -9973,9 +9982,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G154" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/richard-smith-refract</t>
+      <c r="G154" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/richard-smith-refract</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -9990,7 +9999,7 @@
       </c>
       <c r="J154" s="3" t="inlineStr"/>
       <c r="K154" s="3" t="inlineStr"/>
-      <c r="L154" s="9" t="inlineStr">
+      <c r="L154" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -10035,9 +10044,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G155" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/ezevidra</t>
+      <c r="G155" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ezevidra</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -10052,7 +10061,7 @@
       </c>
       <c r="J155" s="3" t="inlineStr"/>
       <c r="K155" s="3" t="inlineStr"/>
-      <c r="L155" s="9" t="inlineStr">
+      <c r="L155" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -10097,9 +10106,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G156" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/robhayward</t>
+      <c r="G156" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/robhayward</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -10114,7 +10123,7 @@
       </c>
       <c r="J156" s="3" t="inlineStr"/>
       <c r="K156" s="3" t="inlineStr"/>
-      <c r="L156" s="9" t="inlineStr">
+      <c r="L156" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -10159,9 +10168,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G157" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/iqbalwahhab</t>
+      <c r="G157" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/iqbalwahhab</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -10176,7 +10185,7 @@
       </c>
       <c r="J157" s="3" t="inlineStr"/>
       <c r="K157" s="3" t="inlineStr"/>
-      <c r="L157" s="9" t="inlineStr">
+      <c r="L157" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -10221,9 +10230,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G158" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/tobyburgess</t>
+      <c r="G158" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tobyburgess</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -10238,7 +10247,7 @@
       </c>
       <c r="J158" s="3" t="inlineStr"/>
       <c r="K158" s="3" t="inlineStr"/>
-      <c r="L158" s="9" t="inlineStr">
+      <c r="L158" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -10283,9 +10292,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G159" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/alexpolizzi</t>
+      <c r="G159" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alexpolizzi</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -10300,7 +10309,7 @@
       </c>
       <c r="J159" s="3" t="inlineStr"/>
       <c r="K159" s="3" t="inlineStr"/>
-      <c r="L159" s="9" t="inlineStr">
+      <c r="L159" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -10345,9 +10354,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G160" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/lucynoble</t>
+      <c r="G160" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lucynoble</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
@@ -10362,7 +10371,7 @@
       </c>
       <c r="J160" s="3" t="inlineStr"/>
       <c r="K160" s="3" t="inlineStr"/>
-      <c r="L160" s="9" t="inlineStr">
+      <c r="L160" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -10407,9 +10416,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G161" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/oliverhansard</t>
+      <c r="G161" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/oliverhansard</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -10424,7 +10433,7 @@
       </c>
       <c r="J161" s="3" t="inlineStr"/>
       <c r="K161" s="3" t="inlineStr"/>
-      <c r="L161" s="9" t="inlineStr">
+      <c r="L161" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -10469,9 +10478,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G162" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/peterharrison</t>
+      <c r="G162" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/peterharrison</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
@@ -10486,7 +10495,7 @@
       </c>
       <c r="J162" s="3" t="inlineStr"/>
       <c r="K162" s="3" t="inlineStr"/>
-      <c r="L162" s="9" t="inlineStr">
+      <c r="L162" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -10531,9 +10540,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G163" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/reshmasohoni</t>
+      <c r="G163" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/reshmasohoni</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
@@ -10548,7 +10557,7 @@
       </c>
       <c r="J163" s="3" t="inlineStr"/>
       <c r="K163" s="3" t="inlineStr"/>
-      <c r="L163" s="9" t="inlineStr">
+      <c r="L163" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -10593,9 +10602,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G164" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/margaret-heffernan</t>
+      <c r="G164" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/margaret-heffernan</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -10610,7 +10619,7 @@
       </c>
       <c r="J164" s="3" t="inlineStr"/>
       <c r="K164" s="3" t="inlineStr"/>
-      <c r="L164" s="9" t="inlineStr">
+      <c r="L164" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -10655,9 +10664,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G165" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/stefanstern</t>
+      <c r="G165" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/stefanstern</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -10672,7 +10681,7 @@
       </c>
       <c r="J165" s="3" t="inlineStr"/>
       <c r="K165" s="3" t="inlineStr"/>
-      <c r="L165" s="9" t="inlineStr">
+      <c r="L165" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -10717,9 +10726,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G166" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/stephenheppell</t>
+      <c r="G166" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/stephenheppell</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -10734,7 +10743,7 @@
       </c>
       <c r="J166" s="3" t="inlineStr"/>
       <c r="K166" s="3" t="inlineStr"/>
-      <c r="L166" s="9" t="inlineStr">
+      <c r="L166" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -10779,9 +10788,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G167" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/deanwilson-seven20</t>
+      <c r="G167" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/deanwilson-seven20</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -10796,7 +10805,7 @@
       </c>
       <c r="J167" s="3" t="inlineStr"/>
       <c r="K167" s="3" t="inlineStr"/>
-      <c r="L167" s="9" t="inlineStr">
+      <c r="L167" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -10841,9 +10850,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G168" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/lukesherran</t>
+      <c r="G168" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lukesherran</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -10858,7 +10867,7 @@
       </c>
       <c r="J168" s="3" t="inlineStr"/>
       <c r="K168" s="3" t="inlineStr"/>
-      <c r="L168" s="9" t="inlineStr">
+      <c r="L168" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -10903,9 +10912,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G169" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/siobhanosullivan</t>
+      <c r="G169" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/siobhanosullivan</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -10920,7 +10929,7 @@
       </c>
       <c r="J169" s="3" t="inlineStr"/>
       <c r="K169" s="3" t="inlineStr"/>
-      <c r="L169" s="9" t="inlineStr">
+      <c r="L169" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -10965,9 +10974,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G170" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/fionaczerniawska</t>
+      <c r="G170" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fionaczerniawska</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -10982,7 +10991,7 @@
       </c>
       <c r="J170" s="3" t="inlineStr"/>
       <c r="K170" s="3" t="inlineStr"/>
-      <c r="L170" s="9" t="inlineStr">
+      <c r="L170" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -11027,9 +11036,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G171" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/emostaque</t>
+      <c r="G171" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/emostaque</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -11044,7 +11053,7 @@
       </c>
       <c r="J171" s="3" t="inlineStr"/>
       <c r="K171" s="3" t="inlineStr"/>
-      <c r="L171" s="9" t="inlineStr">
+      <c r="L171" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -11089,9 +11098,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G172" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/mickwalker</t>
+      <c r="G172" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mickwalker</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -11106,7 +11115,7 @@
       </c>
       <c r="J172" s="3" t="inlineStr"/>
       <c r="K172" s="3" t="inlineStr"/>
-      <c r="L172" s="9" t="inlineStr">
+      <c r="L172" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -11151,9 +11160,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G173" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/katrinacollier</t>
+      <c r="G173" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/katrinacollier</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -11168,7 +11177,7 @@
       </c>
       <c r="J173" s="3" t="inlineStr"/>
       <c r="K173" s="3" t="inlineStr"/>
-      <c r="L173" s="9" t="inlineStr">
+      <c r="L173" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -11213,9 +11222,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G174" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/roblaw-trunki</t>
+      <c r="G174" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/roblaw-trunki</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -11230,7 +11239,7 @@
       </c>
       <c r="J174" s="3" t="inlineStr"/>
       <c r="K174" s="3" t="inlineStr"/>
-      <c r="L174" s="9" t="inlineStr">
+      <c r="L174" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -11275,9 +11284,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G175" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/anilagarwal</t>
+      <c r="G175" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/anilagarwal</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
@@ -11292,7 +11301,7 @@
       </c>
       <c r="J175" s="3" t="inlineStr"/>
       <c r="K175" s="3" t="inlineStr"/>
-      <c r="L175" s="9" t="inlineStr">
+      <c r="L175" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -11337,9 +11346,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G176" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/rbranson</t>
+      <c r="G176" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rbranson</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
@@ -11354,7 +11363,7 @@
       </c>
       <c r="J176" s="3" t="inlineStr"/>
       <c r="K176" s="3" t="inlineStr"/>
-      <c r="L176" s="9" t="inlineStr">
+      <c r="L176" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -11399,9 +11408,9 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G177" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/tejlalvani</t>
+      <c r="G177" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tejlalvani</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -11416,7 +11425,7 @@
       </c>
       <c r="J177" s="3" t="inlineStr"/>
       <c r="K177" s="3" t="inlineStr"/>
-      <c r="L177" s="9" t="inlineStr">
+      <c r="L177" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -11461,9 +11470,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G178" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/bradhargreaves</t>
+      <c r="G178" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/bradhargreaves</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
@@ -11478,7 +11487,7 @@
       </c>
       <c r="J178" s="3" t="inlineStr"/>
       <c r="K178" s="3" t="inlineStr"/>
-      <c r="L178" s="8" t="inlineStr">
+      <c r="L178" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -11523,9 +11532,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G179" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/barbaracorcoran</t>
+      <c r="G179" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/barbaracorcoran</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
@@ -11540,7 +11549,7 @@
       </c>
       <c r="J179" s="3" t="inlineStr"/>
       <c r="K179" s="3" t="inlineStr"/>
-      <c r="L179" s="8" t="inlineStr">
+      <c r="L179" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -11585,9 +11594,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G180" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/andyflorance</t>
+      <c r="G180" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/andyflorance</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
@@ -11602,7 +11611,7 @@
       </c>
       <c r="J180" s="3" t="inlineStr"/>
       <c r="K180" s="3" t="inlineStr"/>
-      <c r="L180" s="8" t="inlineStr">
+      <c r="L180" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -11647,9 +11656,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G181" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/ashkanzandieh</t>
+      <c r="G181" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ashkanzandieh</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
@@ -11664,7 +11673,7 @@
       </c>
       <c r="J181" s="3" t="inlineStr"/>
       <c r="K181" s="3" t="inlineStr"/>
-      <c r="L181" s="8" t="inlineStr">
+      <c r="L181" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -11709,9 +11718,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G182" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/cliapeters</t>
+      <c r="G182" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/cliapeters</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
@@ -11726,7 +11735,7 @@
       </c>
       <c r="J182" s="3" t="inlineStr"/>
       <c r="K182" s="3" t="inlineStr"/>
-      <c r="L182" s="8" t="inlineStr">
+      <c r="L182" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -11771,9 +11780,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G183" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/glennsanford</t>
+      <c r="G183" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/glennsanford</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
@@ -11788,7 +11797,7 @@
       </c>
       <c r="J183" s="3" t="inlineStr"/>
       <c r="K183" s="3" t="inlineStr"/>
-      <c r="L183" s="8" t="inlineStr">
+      <c r="L183" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -11833,9 +11842,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G184" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/grahamstephan</t>
+      <c r="G184" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/grahamstephan</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
@@ -11850,7 +11859,7 @@
       </c>
       <c r="J184" s="3" t="inlineStr"/>
       <c r="K184" s="3" t="inlineStr"/>
-      <c r="L184" s="8" t="inlineStr">
+      <c r="L184" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -11895,9 +11904,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G185" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/travisskelly</t>
+      <c r="G185" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/travisskelly</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -11912,7 +11921,7 @@
       </c>
       <c r="J185" s="3" t="inlineStr"/>
       <c r="K185" s="3" t="inlineStr"/>
-      <c r="L185" s="8" t="inlineStr">
+      <c r="L185" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -11957,9 +11966,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G186" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/hamidmoghadam</t>
+      <c r="G186" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hamidmoghadam</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
@@ -11974,7 +11983,7 @@
       </c>
       <c r="J186" s="3" t="inlineStr"/>
       <c r="K186" s="3" t="inlineStr"/>
-      <c r="L186" s="8" t="inlineStr">
+      <c r="L186" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -12019,9 +12028,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G187" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/company/propy-inc</t>
+      <c r="G187" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/propy-inc</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
@@ -12036,7 +12045,7 @@
       </c>
       <c r="J187" s="3" t="inlineStr"/>
       <c r="K187" s="3" t="inlineStr"/>
-      <c r="L187" s="8" t="inlineStr">
+      <c r="L187" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -12081,9 +12090,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G188" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/kubaj</t>
+      <c r="G188" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kubaj</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -12098,7 +12107,7 @@
       </c>
       <c r="J188" s="3" t="inlineStr"/>
       <c r="K188" s="3" t="inlineStr"/>
-      <c r="L188" s="8" t="inlineStr">
+      <c r="L188" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -12143,9 +12152,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G189" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/drorpoleg</t>
+      <c r="G189" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/drorpoleg</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -12160,7 +12169,7 @@
       </c>
       <c r="J189" s="3" t="inlineStr"/>
       <c r="K189" s="3" t="inlineStr"/>
-      <c r="L189" s="8" t="inlineStr">
+      <c r="L189" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -12205,9 +12214,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G190" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/ryanserhant</t>
+      <c r="G190" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ryanserhant</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
@@ -12222,7 +12231,7 @@
       </c>
       <c r="J190" s="3" t="inlineStr"/>
       <c r="K190" s="3" t="inlineStr"/>
-      <c r="L190" s="8" t="inlineStr">
+      <c r="L190" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -12267,9 +12276,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G191" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/david-simon-spg</t>
+      <c r="G191" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/david-simon-spg</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -12284,7 +12293,7 @@
       </c>
       <c r="J191" s="3" t="inlineStr"/>
       <c r="K191" s="3" t="inlineStr"/>
-      <c r="L191" s="8" t="inlineStr">
+      <c r="L191" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -12329,9 +12338,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G192" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/pacemorby</t>
+      <c r="G192" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/pacemorby</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -12346,7 +12355,7 @@
       </c>
       <c r="J192" s="3" t="inlineStr"/>
       <c r="K192" s="3" t="inlineStr"/>
-      <c r="L192" s="8" t="inlineStr">
+      <c r="L192" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -12391,9 +12400,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G193" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/mauricio-umansky</t>
+      <c r="G193" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mauricio-umansky</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
@@ -12408,7 +12417,7 @@
       </c>
       <c r="J193" s="3" t="inlineStr"/>
       <c r="K193" s="3" t="inlineStr"/>
-      <c r="L193" s="8" t="inlineStr">
+      <c r="L193" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -12453,9 +12462,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G194" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/mannykhoshbin</t>
+      <c r="G194" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mannykhoshbin</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
@@ -12470,7 +12479,7 @@
       </c>
       <c r="J194" s="3" t="inlineStr"/>
       <c r="K194" s="3" t="inlineStr"/>
-      <c r="L194" s="8" t="inlineStr">
+      <c r="L194" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -12515,9 +12524,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G195" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/tomferry</t>
+      <c r="G195" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tomferry</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
@@ -12532,7 +12541,7 @@
       </c>
       <c r="J195" s="3" t="inlineStr"/>
       <c r="K195" s="3" t="inlineStr"/>
-      <c r="L195" s="8" t="inlineStr">
+      <c r="L195" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -12577,9 +12586,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G196" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/spencerrascoff</t>
+      <c r="G196" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/spencerrascoff</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -12594,7 +12603,7 @@
       </c>
       <c r="J196" s="3" t="inlineStr"/>
       <c r="K196" s="3" t="inlineStr"/>
-      <c r="L196" s="8" t="inlineStr">
+      <c r="L196" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -12639,9 +12648,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G197" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/keenan-salesperson</t>
+      <c r="G197" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/keenan-salesperson</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -12656,7 +12665,7 @@
       </c>
       <c r="J197" s="3" t="inlineStr"/>
       <c r="K197" s="3" t="inlineStr"/>
-      <c r="L197" s="9" t="inlineStr">
+      <c r="L197" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -12701,9 +12710,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G198" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/behorowitz</t>
+      <c r="G198" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/behorowitz</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -12718,7 +12727,7 @@
       </c>
       <c r="J198" s="3" t="inlineStr"/>
       <c r="K198" s="3" t="inlineStr"/>
-      <c r="L198" s="9" t="inlineStr">
+      <c r="L198" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -12763,9 +12772,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G199" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/company/aeg-presents</t>
+      <c r="G199" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/aeg-presents</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -12780,7 +12789,7 @@
       </c>
       <c r="J199" s="3" t="inlineStr"/>
       <c r="K199" s="3" t="inlineStr"/>
-      <c r="L199" s="9" t="inlineStr">
+      <c r="L199" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -12825,9 +12834,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G200" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/drewmclellan</t>
+      <c r="G200" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/drewmclellan</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
@@ -12842,7 +12851,7 @@
       </c>
       <c r="J200" s="3" t="inlineStr"/>
       <c r="K200" s="3" t="inlineStr"/>
-      <c r="L200" s="9" t="inlineStr">
+      <c r="L200" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -12887,9 +12896,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G201" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/jasonswenk</t>
+      <c r="G201" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jasonswenk</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -12904,7 +12913,7 @@
       </c>
       <c r="J201" s="3" t="inlineStr"/>
       <c r="K201" s="3" t="inlineStr"/>
-      <c r="L201" s="9" t="inlineStr">
+      <c r="L201" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -12949,9 +12958,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G202" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/liorbendavid</t>
+      <c r="G202" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/liorbendavid</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
@@ -12966,7 +12975,7 @@
       </c>
       <c r="J202" s="3" t="inlineStr"/>
       <c r="K202" s="3" t="inlineStr"/>
-      <c r="L202" s="9" t="inlineStr">
+      <c r="L202" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -13011,9 +13020,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G203" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/alliekmiller</t>
+      <c r="G203" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alliekmiller</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
@@ -13028,7 +13037,7 @@
       </c>
       <c r="J203" s="3" t="inlineStr"/>
       <c r="K203" s="3" t="inlineStr"/>
-      <c r="L203" s="9" t="inlineStr">
+      <c r="L203" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -13073,9 +13082,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G204" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/lars-schmidt</t>
+      <c r="G204" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lars-schmidt</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -13090,7 +13099,7 @@
       </c>
       <c r="J204" s="3" t="inlineStr"/>
       <c r="K204" s="3" t="inlineStr"/>
-      <c r="L204" s="9" t="inlineStr">
+      <c r="L204" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -13135,9 +13144,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G205" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/matthewjeffery</t>
+      <c r="G205" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/matthewjeffery</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
@@ -13152,7 +13161,7 @@
       </c>
       <c r="J205" s="3" t="inlineStr"/>
       <c r="K205" s="3" t="inlineStr"/>
-      <c r="L205" s="9" t="inlineStr">
+      <c r="L205" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -13197,9 +13206,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G206" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/drewsanocki</t>
+      <c r="G206" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/drewsanocki</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -13214,7 +13223,7 @@
       </c>
       <c r="J206" s="3" t="inlineStr"/>
       <c r="K206" s="3" t="inlineStr"/>
-      <c r="L206" s="9" t="inlineStr">
+      <c r="L206" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -13259,9 +13268,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G207" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/annscher</t>
+      <c r="G207" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/annscher</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
@@ -13276,7 +13285,7 @@
       </c>
       <c r="J207" s="3" t="inlineStr"/>
       <c r="K207" s="3" t="inlineStr"/>
-      <c r="L207" s="9" t="inlineStr">
+      <c r="L207" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -13321,9 +13330,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G208" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/irvingzoff</t>
+      <c r="G208" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/irvingzoff</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
@@ -13338,7 +13347,7 @@
       </c>
       <c r="J208" s="3" t="inlineStr"/>
       <c r="K208" s="3" t="inlineStr"/>
-      <c r="L208" s="9" t="inlineStr">
+      <c r="L208" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -13383,9 +13392,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G209" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/iannarino</t>
+      <c r="G209" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/iannarino</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
@@ -13400,7 +13409,7 @@
       </c>
       <c r="J209" s="3" t="inlineStr"/>
       <c r="K209" s="3" t="inlineStr"/>
-      <c r="L209" s="9" t="inlineStr">
+      <c r="L209" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -13445,9 +13454,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G210" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/carlrichards</t>
+      <c r="G210" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/carlrichards</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
@@ -13462,7 +13471,7 @@
       </c>
       <c r="J210" s="3" t="inlineStr"/>
       <c r="K210" s="3" t="inlineStr"/>
-      <c r="L210" s="9" t="inlineStr">
+      <c r="L210" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -13507,9 +13516,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G211" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/ryanholiday</t>
+      <c r="G211" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ryanholiday</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr">
@@ -13524,7 +13533,7 @@
       </c>
       <c r="J211" s="3" t="inlineStr"/>
       <c r="K211" s="3" t="inlineStr"/>
-      <c r="L211" s="9" t="inlineStr">
+      <c r="L211" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -13569,9 +13578,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G212" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/brenebrown</t>
+      <c r="G212" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/brenebrown</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
@@ -13586,7 +13595,7 @@
       </c>
       <c r="J212" s="3" t="inlineStr"/>
       <c r="K212" s="3" t="inlineStr"/>
-      <c r="L212" s="9" t="inlineStr">
+      <c r="L212" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -13631,9 +13640,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G213" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/trish-bertuzzi</t>
+      <c r="G213" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/trish-bertuzzi</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
@@ -13648,7 +13657,7 @@
       </c>
       <c r="J213" s="3" t="inlineStr"/>
       <c r="K213" s="3" t="inlineStr"/>
-      <c r="L213" s="9" t="inlineStr">
+      <c r="L213" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -13693,9 +13702,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G214" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/raydalio</t>
+      <c r="G214" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/raydalio</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr">
@@ -13710,7 +13719,7 @@
       </c>
       <c r="J214" s="3" t="inlineStr"/>
       <c r="K214" s="3" t="inlineStr"/>
-      <c r="L214" s="9" t="inlineStr">
+      <c r="L214" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -13755,9 +13764,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G215" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/ruchika-tulshyan</t>
+      <c r="G215" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ruchika-tulshyan</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr">
@@ -13772,7 +13781,7 @@
       </c>
       <c r="J215" s="3" t="inlineStr"/>
       <c r="K215" s="3" t="inlineStr"/>
-      <c r="L215" s="9" t="inlineStr">
+      <c r="L215" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -13817,9 +13826,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G216" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/davidrubenstein</t>
+      <c r="G216" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/davidrubenstein</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
@@ -13834,7 +13843,7 @@
       </c>
       <c r="J216" s="3" t="inlineStr"/>
       <c r="K216" s="3" t="inlineStr"/>
-      <c r="L216" s="9" t="inlineStr">
+      <c r="L216" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -13879,9 +13888,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G217" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/deepakchopra</t>
+      <c r="G217" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/deepakchopra</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr">
@@ -13896,7 +13905,7 @@
       </c>
       <c r="J217" s="3" t="inlineStr"/>
       <c r="K217" s="3" t="inlineStr"/>
-      <c r="L217" s="9" t="inlineStr">
+      <c r="L217" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -13941,9 +13950,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G218" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/mollydibianca</t>
+      <c r="G218" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mollydibianca</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
@@ -13958,7 +13967,7 @@
       </c>
       <c r="J218" s="3" t="inlineStr"/>
       <c r="K218" s="3" t="inlineStr"/>
-      <c r="L218" s="9" t="inlineStr">
+      <c r="L218" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -14003,9 +14012,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G219" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/michaelbhorn</t>
+      <c r="G219" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/michaelbhorn</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr">
@@ -14020,7 +14029,7 @@
       </c>
       <c r="J219" s="3" t="inlineStr"/>
       <c r="K219" s="3" t="inlineStr"/>
-      <c r="L219" s="9" t="inlineStr">
+      <c r="L219" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -14065,9 +14074,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G220" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/morganjingram</t>
+      <c r="G220" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/morganjingram</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
@@ -14082,7 +14091,7 @@
       </c>
       <c r="J220" s="3" t="inlineStr"/>
       <c r="K220" s="3" t="inlineStr"/>
-      <c r="L220" s="9" t="inlineStr">
+      <c r="L220" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -14127,9 +14136,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G221" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/morganhousel</t>
+      <c r="G221" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/morganhousel</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -14144,7 +14153,7 @@
       </c>
       <c r="J221" s="3" t="inlineStr"/>
       <c r="K221" s="3" t="inlineStr"/>
-      <c r="L221" s="9" t="inlineStr">
+      <c r="L221" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -14189,9 +14198,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G222" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/poojajainlink</t>
+      <c r="G222" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/poojajainlink</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">
@@ -14206,7 +14215,7 @@
       </c>
       <c r="J222" s="3" t="inlineStr"/>
       <c r="K222" s="3" t="inlineStr"/>
-      <c r="L222" s="9" t="inlineStr">
+      <c r="L222" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -14251,9 +14260,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G223" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/ericadhawan</t>
+      <c r="G223" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ericadhawan</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
@@ -14268,7 +14277,7 @@
       </c>
       <c r="J223" s="3" t="inlineStr"/>
       <c r="K223" s="3" t="inlineStr"/>
-      <c r="L223" s="9" t="inlineStr">
+      <c r="L223" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -14313,9 +14322,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G224" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/daphnekoller</t>
+      <c r="G224" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/daphnekoller</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
@@ -14330,7 +14339,7 @@
       </c>
       <c r="J224" s="3" t="inlineStr"/>
       <c r="K224" s="3" t="inlineStr"/>
-      <c r="L224" s="9" t="inlineStr">
+      <c r="L224" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -14375,9 +14384,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G225" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/jonathandaniel</t>
+      <c r="G225" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jonathandaniel</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -14392,7 +14401,7 @@
       </c>
       <c r="J225" s="3" t="inlineStr"/>
       <c r="K225" s="3" t="inlineStr"/>
-      <c r="L225" s="9" t="inlineStr">
+      <c r="L225" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -14437,9 +14446,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G226" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/jhagel</t>
+      <c r="G226" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jhagel</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
@@ -14454,7 +14463,7 @@
       </c>
       <c r="J226" s="3" t="inlineStr"/>
       <c r="K226" s="3" t="inlineStr"/>
-      <c r="L226" s="9" t="inlineStr">
+      <c r="L226" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -14499,9 +14508,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G227" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/whitneyjohnson</t>
+      <c r="G227" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/whitneyjohnson</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -14516,7 +14525,7 @@
       </c>
       <c r="J227" s="3" t="inlineStr"/>
       <c r="K227" s="3" t="inlineStr"/>
-      <c r="L227" s="9" t="inlineStr">
+      <c r="L227" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -14561,9 +14570,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G228" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/peterattiamd</t>
+      <c r="G228" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/peterattiamd</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -14578,7 +14587,7 @@
       </c>
       <c r="J228" s="3" t="inlineStr"/>
       <c r="K228" s="3" t="inlineStr"/>
-      <c r="L228" s="9" t="inlineStr">
+      <c r="L228" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -14623,9 +14632,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G229" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/jocko-willink</t>
+      <c r="G229" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jocko-willink</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -14640,7 +14649,7 @@
       </c>
       <c r="J229" s="3" t="inlineStr"/>
       <c r="K229" s="3" t="inlineStr"/>
-      <c r="L229" s="9" t="inlineStr">
+      <c r="L229" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -14685,9 +14694,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G230" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/ricedelman</t>
+      <c r="G230" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ricedelman</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
@@ -14702,7 +14711,7 @@
       </c>
       <c r="J230" s="3" t="inlineStr"/>
       <c r="K230" s="3" t="inlineStr"/>
-      <c r="L230" s="9" t="inlineStr">
+      <c r="L230" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -14747,9 +14756,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G231" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/salliekrawcheck</t>
+      <c r="G231" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/salliekrawcheck</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -14764,7 +14773,7 @@
       </c>
       <c r="J231" s="3" t="inlineStr"/>
       <c r="K231" s="3" t="inlineStr"/>
-      <c r="L231" s="9" t="inlineStr">
+      <c r="L231" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -14809,9 +14818,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G232" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/samzell</t>
+      <c r="G232" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/samzell</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -14826,7 +14835,7 @@
       </c>
       <c r="J232" s="3" t="inlineStr"/>
       <c r="K232" s="3" t="inlineStr"/>
-      <c r="L232" s="9" t="inlineStr">
+      <c r="L232" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -14871,9 +14880,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G233" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/meerakhgandhi</t>
+      <c r="G233" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/meerakhgandhi</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
@@ -14888,7 +14897,7 @@
       </c>
       <c r="J233" s="3" t="inlineStr"/>
       <c r="K233" s="3" t="inlineStr"/>
-      <c r="L233" s="9" t="inlineStr">
+      <c r="L233" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -14933,9 +14942,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G234" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/astroteller</t>
+      <c r="G234" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/astroteller</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
@@ -14950,7 +14959,7 @@
       </c>
       <c r="J234" s="3" t="inlineStr"/>
       <c r="K234" s="3" t="inlineStr"/>
-      <c r="L234" s="9" t="inlineStr">
+      <c r="L234" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -14995,9 +15004,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G235" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/reidhoffman</t>
+      <c r="G235" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/reidhoffman</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -15012,7 +15021,7 @@
       </c>
       <c r="J235" s="3" t="inlineStr"/>
       <c r="K235" s="3" t="inlineStr"/>
-      <c r="L235" s="9" t="inlineStr">
+      <c r="L235" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -15057,9 +15066,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G236" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/sangramvajre</t>
+      <c r="G236" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sangramvajre</t>
         </is>
       </c>
       <c r="H236" s="2" t="inlineStr">
@@ -15074,7 +15083,7 @@
       </c>
       <c r="J236" s="3" t="inlineStr"/>
       <c r="K236" s="3" t="inlineStr"/>
-      <c r="L236" s="9" t="inlineStr">
+      <c r="L236" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -15119,9 +15128,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G237" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/amyedmondson</t>
+      <c r="G237" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/amyedmondson</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -15136,7 +15145,7 @@
       </c>
       <c r="J237" s="3" t="inlineStr"/>
       <c r="K237" s="3" t="inlineStr"/>
-      <c r="L237" s="9" t="inlineStr">
+      <c r="L237" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -15181,9 +15190,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G238" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/stevengoldstein</t>
+      <c r="G238" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/stevengoldstein</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -15198,7 +15207,7 @@
       </c>
       <c r="J238" s="3" t="inlineStr"/>
       <c r="K238" s="3" t="inlineStr"/>
-      <c r="L238" s="9" t="inlineStr">
+      <c r="L238" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -15243,9 +15252,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G239" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/hunterwalk</t>
+      <c r="G239" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hunterwalk</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr">
@@ -15260,7 +15269,7 @@
       </c>
       <c r="J239" s="3" t="inlineStr"/>
       <c r="K239" s="3" t="inlineStr"/>
-      <c r="L239" s="9" t="inlineStr">
+      <c r="L239" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -15305,9 +15314,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G240" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/leahhouston</t>
+      <c r="G240" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/leahhouston</t>
         </is>
       </c>
       <c r="H240" s="2" t="inlineStr">
@@ -15322,7 +15331,7 @@
       </c>
       <c r="J240" s="3" t="inlineStr"/>
       <c r="K240" s="3" t="inlineStr"/>
-      <c r="L240" s="9" t="inlineStr">
+      <c r="L240" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -15367,9 +15376,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G241" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/dharmesh</t>
+      <c r="G241" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dharmesh</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr">
@@ -15384,7 +15393,7 @@
       </c>
       <c r="J241" s="3" t="inlineStr"/>
       <c r="K241" s="3" t="inlineStr"/>
-      <c r="L241" s="9" t="inlineStr">
+      <c r="L241" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -15429,9 +15438,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G242" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/lizryan</t>
+      <c r="G242" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lizryan</t>
         </is>
       </c>
       <c r="H242" s="2" t="inlineStr">
@@ -15446,7 +15455,7 @@
       </c>
       <c r="J242" s="3" t="inlineStr"/>
       <c r="K242" s="3" t="inlineStr"/>
-      <c r="L242" s="9" t="inlineStr">
+      <c r="L242" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -15491,9 +15500,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G243" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/elizabethyin</t>
+      <c r="G243" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/elizabethyin</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">
@@ -15508,7 +15517,7 @@
       </c>
       <c r="J243" s="3" t="inlineStr"/>
       <c r="K243" s="3" t="inlineStr"/>
-      <c r="L243" s="9" t="inlineStr">
+      <c r="L243" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -15553,9 +15562,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G244" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/scooterbraun</t>
+      <c r="G244" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/scooterbraun</t>
         </is>
       </c>
       <c r="H244" s="2" t="inlineStr">
@@ -15570,7 +15579,7 @@
       </c>
       <c r="J244" s="3" t="inlineStr"/>
       <c r="K244" s="3" t="inlineStr"/>
-      <c r="L244" s="9" t="inlineStr">
+      <c r="L244" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -15615,9 +15624,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G245" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/marcus-sheridan</t>
+      <c r="G245" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/marcus-sheridan</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
@@ -15632,7 +15641,7 @@
       </c>
       <c r="J245" s="3" t="inlineStr"/>
       <c r="K245" s="3" t="inlineStr"/>
-      <c r="L245" s="9" t="inlineStr">
+      <c r="L245" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -15677,9 +15686,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G246" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/nickstorch-iag</t>
+      <c r="G246" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nickstorch-iag</t>
         </is>
       </c>
       <c r="H246" s="2" t="inlineStr">
@@ -15694,7 +15703,7 @@
       </c>
       <c r="J246" s="3" t="inlineStr"/>
       <c r="K246" s="3" t="inlineStr"/>
-      <c r="L246" s="9" t="inlineStr">
+      <c r="L246" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -15739,9 +15748,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G247" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/erinmeezan</t>
+      <c r="G247" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/erinmeezan</t>
         </is>
       </c>
       <c r="H247" s="2" t="inlineStr">
@@ -15756,7 +15765,7 @@
       </c>
       <c r="J247" s="3" t="inlineStr"/>
       <c r="K247" s="3" t="inlineStr"/>
-      <c r="L247" s="9" t="inlineStr">
+      <c r="L247" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -15801,9 +15810,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G248" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/johnbarrows</t>
+      <c r="G248" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/johnbarrows</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
@@ -15818,7 +15827,7 @@
       </c>
       <c r="J248" s="3" t="inlineStr"/>
       <c r="K248" s="3" t="inlineStr"/>
-      <c r="L248" s="9" t="inlineStr">
+      <c r="L248" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -15863,9 +15872,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G249" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/jenniferbrownnyc</t>
+      <c r="G249" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jenniferbrownnyc</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr">
@@ -15880,7 +15889,7 @@
       </c>
       <c r="J249" s="3" t="inlineStr"/>
       <c r="K249" s="3" t="inlineStr"/>
-      <c r="L249" s="9" t="inlineStr">
+      <c r="L249" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -15925,9 +15934,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G250" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/salmankhan</t>
+      <c r="G250" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/salmankhan</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr">
@@ -15942,7 +15951,7 @@
       </c>
       <c r="J250" s="3" t="inlineStr"/>
       <c r="K250" s="3" t="inlineStr"/>
-      <c r="L250" s="9" t="inlineStr">
+      <c r="L250" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -15987,9 +15996,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G251" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/michaelkitces</t>
+      <c r="G251" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/michaelkitces</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
@@ -16004,7 +16013,7 @@
       </c>
       <c r="J251" s="3" t="inlineStr"/>
       <c r="K251" s="3" t="inlineStr"/>
-      <c r="L251" s="9" t="inlineStr">
+      <c r="L251" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -16049,9 +16058,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G252" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/sbbrowne</t>
+      <c r="G252" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sbbrowne</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr">
@@ -16066,7 +16075,7 @@
       </c>
       <c r="J252" s="3" t="inlineStr"/>
       <c r="K252" s="3" t="inlineStr"/>
-      <c r="L252" s="9" t="inlineStr">
+      <c r="L252" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -16111,9 +16120,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G253" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/michaelrapino</t>
+      <c r="G253" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/michaelrapino</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr">
@@ -16128,7 +16137,7 @@
       </c>
       <c r="J253" s="3" t="inlineStr"/>
       <c r="K253" s="3" t="inlineStr"/>
-      <c r="L253" s="9" t="inlineStr">
+      <c r="L253" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -16173,9 +16182,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G254" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/marieforleo</t>
+      <c r="G254" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/marieforleo</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
@@ -16190,7 +16199,7 @@
       </c>
       <c r="J254" s="3" t="inlineStr"/>
       <c r="K254" s="3" t="inlineStr"/>
-      <c r="L254" s="9" t="inlineStr">
+      <c r="L254" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -16235,9 +16244,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G255" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/paulroetzer</t>
+      <c r="G255" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/paulroetzer</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
@@ -16252,7 +16261,7 @@
       </c>
       <c r="J255" s="3" t="inlineStr"/>
       <c r="K255" s="3" t="inlineStr"/>
-      <c r="L255" s="9" t="inlineStr">
+      <c r="L255" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -16297,9 +16306,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G256" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/annhandley</t>
+      <c r="G256" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/annhandley</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
@@ -16314,7 +16323,7 @@
       </c>
       <c r="J256" s="3" t="inlineStr"/>
       <c r="K256" s="3" t="inlineStr"/>
-      <c r="L256" s="9" t="inlineStr">
+      <c r="L256" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -16359,9 +16368,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G257" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/weskao</t>
+      <c r="G257" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/weskao</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
@@ -16376,7 +16385,7 @@
       </c>
       <c r="J257" s="3" t="inlineStr"/>
       <c r="K257" s="3" t="inlineStr"/>
-      <c r="L257" s="9" t="inlineStr">
+      <c r="L257" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -16421,9 +16430,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G258" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/ritamcgrath</t>
+      <c r="G258" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ritamcgrath</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
@@ -16438,7 +16447,7 @@
       </c>
       <c r="J258" s="3" t="inlineStr"/>
       <c r="K258" s="3" t="inlineStr"/>
-      <c r="L258" s="9" t="inlineStr">
+      <c r="L258" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -16483,9 +16492,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G259" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/vernamyers</t>
+      <c r="G259" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vernamyers</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr">
@@ -16500,7 +16509,7 @@
       </c>
       <c r="J259" s="3" t="inlineStr"/>
       <c r="K259" s="3" t="inlineStr"/>
-      <c r="L259" s="9" t="inlineStr">
+      <c r="L259" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -16545,9 +16554,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G260" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/mikeweinberg</t>
+      <c r="G260" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mikeweinberg</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
@@ -16562,7 +16571,7 @@
       </c>
       <c r="J260" s="3" t="inlineStr"/>
       <c r="K260" s="3" t="inlineStr"/>
-      <c r="L260" s="9" t="inlineStr">
+      <c r="L260" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -16607,9 +16616,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G261" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/nireyal</t>
+      <c r="G261" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nireyal</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
@@ -16624,7 +16633,7 @@
       </c>
       <c r="J261" s="3" t="inlineStr"/>
       <c r="K261" s="3" t="inlineStr"/>
-      <c r="L261" s="9" t="inlineStr">
+      <c r="L261" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -16669,9 +16678,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G262" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/neilkpatel</t>
+      <c r="G262" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/neilkpatel</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr">
@@ -16686,7 +16695,7 @@
       </c>
       <c r="J262" s="3" t="inlineStr"/>
       <c r="K262" s="3" t="inlineStr"/>
-      <c r="L262" s="9" t="inlineStr">
+      <c r="L262" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -16731,9 +16740,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G263" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/jenhsunhuang</t>
+      <c r="G263" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jenhsunhuang</t>
         </is>
       </c>
       <c r="H263" s="2" t="inlineStr">
@@ -16748,7 +16757,7 @@
       </c>
       <c r="J263" s="3" t="inlineStr"/>
       <c r="K263" s="3" t="inlineStr"/>
-      <c r="L263" s="9" t="inlineStr">
+      <c r="L263" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -16793,9 +16802,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G264" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/dollychugh</t>
+      <c r="G264" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dollychugh</t>
         </is>
       </c>
       <c r="H264" s="2" t="inlineStr">
@@ -16810,7 +16819,7 @@
       </c>
       <c r="J264" s="3" t="inlineStr"/>
       <c r="K264" s="3" t="inlineStr"/>
-      <c r="L264" s="9" t="inlineStr">
+      <c r="L264" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -16855,9 +16864,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G265" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/kevin-oleary</t>
+      <c r="G265" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kevin-oleary</t>
         </is>
       </c>
       <c r="H265" s="2" t="inlineStr">
@@ -16872,7 +16881,7 @@
       </c>
       <c r="J265" s="3" t="inlineStr"/>
       <c r="K265" s="3" t="inlineStr"/>
-      <c r="L265" s="9" t="inlineStr">
+      <c r="L265" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -16917,9 +16926,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G266" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/desireemartinez</t>
+      <c r="G266" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/desireemartinez</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr">
@@ -16934,7 +16943,7 @@
       </c>
       <c r="J266" s="3" t="inlineStr"/>
       <c r="K266" s="3" t="inlineStr"/>
-      <c r="L266" s="9" t="inlineStr">
+      <c r="L266" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -16979,9 +16988,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G267" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/sam-altman</t>
+      <c r="G267" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sam-altman</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -16996,7 +17005,7 @@
       </c>
       <c r="J267" s="3" t="inlineStr"/>
       <c r="K267" s="3" t="inlineStr"/>
-      <c r="L267" s="9" t="inlineStr">
+      <c r="L267" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -17041,9 +17050,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G268" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/anthonypompliano</t>
+      <c r="G268" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/anthonypompliano</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -17058,7 +17067,7 @@
       </c>
       <c r="J268" s="3" t="inlineStr"/>
       <c r="K268" s="3" t="inlineStr"/>
-      <c r="L268" s="9" t="inlineStr">
+      <c r="L268" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -17103,9 +17112,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G269" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/troycarter</t>
+      <c r="G269" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/troycarter</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -17120,7 +17129,7 @@
       </c>
       <c r="J269" s="3" t="inlineStr"/>
       <c r="K269" s="3" t="inlineStr"/>
-      <c r="L269" s="9" t="inlineStr">
+      <c r="L269" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -17165,9 +17174,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G270" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/williamtincup</t>
+      <c r="G270" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/williamtincup</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -17182,7 +17191,7 @@
       </c>
       <c r="J270" s="3" t="inlineStr"/>
       <c r="K270" s="3" t="inlineStr"/>
-      <c r="L270" s="9" t="inlineStr">
+      <c r="L270" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -17227,9 +17236,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G271" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/pamdidner</t>
+      <c r="G271" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/pamdidner</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr">
@@ -17244,7 +17253,7 @@
       </c>
       <c r="J271" s="3" t="inlineStr"/>
       <c r="K271" s="3" t="inlineStr"/>
-      <c r="L271" s="9" t="inlineStr">
+      <c r="L271" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -17289,9 +17298,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G272" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/staceygordon</t>
+      <c r="G272" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/staceygordon</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
@@ -17306,7 +17315,7 @@
       </c>
       <c r="J272" s="3" t="inlineStr"/>
       <c r="K272" s="3" t="inlineStr"/>
-      <c r="L272" s="9" t="inlineStr">
+      <c r="L272" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -17351,9 +17360,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G273" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/bencarlson</t>
+      <c r="G273" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/bencarlson</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -17368,7 +17377,7 @@
       </c>
       <c r="J273" s="3" t="inlineStr"/>
       <c r="K273" s="3" t="inlineStr"/>
-      <c r="L273" s="9" t="inlineStr">
+      <c r="L273" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -17413,9 +17422,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G274" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/thereformedbroker</t>
+      <c r="G274" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/thereformedbroker</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -17430,7 +17439,7 @@
       </c>
       <c r="J274" s="3" t="inlineStr"/>
       <c r="K274" s="3" t="inlineStr"/>
-      <c r="L274" s="9" t="inlineStr">
+      <c r="L274" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -17475,9 +17484,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G275" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/tonyrobbins</t>
+      <c r="G275" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tonyrobbins</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr">
@@ -17492,7 +17501,7 @@
       </c>
       <c r="J275" s="3" t="inlineStr"/>
       <c r="K275" s="3" t="inlineStr"/>
-      <c r="L275" s="9" t="inlineStr">
+      <c r="L275" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -17537,9 +17546,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G276" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/cynthiaowyoung</t>
+      <c r="G276" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/cynthiaowyoung</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr">
@@ -17554,7 +17563,7 @@
       </c>
       <c r="J276" s="3" t="inlineStr"/>
       <c r="K276" s="3" t="inlineStr"/>
-      <c r="L276" s="9" t="inlineStr">
+      <c r="L276" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -17599,9 +17608,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G277" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/karlsakas</t>
+      <c r="G277" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/karlsakas</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr">
@@ -17616,7 +17625,7 @@
       </c>
       <c r="J277" s="3" t="inlineStr"/>
       <c r="K277" s="3" t="inlineStr"/>
-      <c r="L277" s="9" t="inlineStr">
+      <c r="L277" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -17661,9 +17670,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G278" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/jebblount</t>
+      <c r="G278" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jebblount</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
@@ -17678,7 +17687,7 @@
       </c>
       <c r="J278" s="3" t="inlineStr"/>
       <c r="K278" s="3" t="inlineStr"/>
-      <c r="L278" s="9" t="inlineStr">
+      <c r="L278" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -17723,9 +17732,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G279" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/tiffanibova</t>
+      <c r="G279" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tiffanibova</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
@@ -17740,7 +17749,7 @@
       </c>
       <c r="J279" s="3" t="inlineStr"/>
       <c r="K279" s="3" t="inlineStr"/>
-      <c r="L279" s="9" t="inlineStr">
+      <c r="L279" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -17785,9 +17794,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G280" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/markwschaefer</t>
+      <c r="G280" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/markwschaefer</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr">
@@ -17802,7 +17811,7 @@
       </c>
       <c r="J280" s="3" t="inlineStr"/>
       <c r="K280" s="3" t="inlineStr"/>
-      <c r="L280" s="9" t="inlineStr">
+      <c r="L280" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -17847,9 +17856,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G281" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/loririchardson</t>
+      <c r="G281" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/loririchardson</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -17864,7 +17873,7 @@
       </c>
       <c r="J281" s="3" t="inlineStr"/>
       <c r="K281" s="3" t="inlineStr"/>
-      <c r="L281" s="9" t="inlineStr">
+      <c r="L281" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -17909,9 +17918,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G282" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/erictopol</t>
+      <c r="G282" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/erictopol</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -17926,7 +17935,7 @@
       </c>
       <c r="J282" s="3" t="inlineStr"/>
       <c r="K282" s="3" t="inlineStr"/>
-      <c r="L282" s="9" t="inlineStr">
+      <c r="L282" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -17971,9 +17980,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G283" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/profgalloway</t>
+      <c r="G283" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/profgalloway</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
@@ -17988,7 +17997,7 @@
       </c>
       <c r="J283" s="3" t="inlineStr"/>
       <c r="K283" s="3" t="inlineStr"/>
-      <c r="L283" s="9" t="inlineStr">
+      <c r="L283" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -18033,9 +18042,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G284" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/ashramos</t>
+      <c r="G284" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ashramos</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
@@ -18050,7 +18059,7 @@
       </c>
       <c r="J284" s="3" t="inlineStr"/>
       <c r="K284" s="3" t="inlineStr"/>
-      <c r="L284" s="9" t="inlineStr">
+      <c r="L284" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -18095,9 +18104,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G285" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/benny-blanco</t>
+      <c r="G285" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/benny-blanco</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
@@ -18112,7 +18121,7 @@
       </c>
       <c r="J285" s="3" t="inlineStr"/>
       <c r="K285" s="3" t="inlineStr"/>
-      <c r="L285" s="9" t="inlineStr">
+      <c r="L285" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -18157,9 +18166,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G286" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/davidmaister</t>
+      <c r="G286" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/davidmaister</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -18174,7 +18183,7 @@
       </c>
       <c r="J286" s="3" t="inlineStr"/>
       <c r="K286" s="3" t="inlineStr"/>
-      <c r="L286" s="9" t="inlineStr">
+      <c r="L286" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -18219,9 +18228,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G287" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/dorieclark</t>
+      <c r="G287" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dorieclark</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -18236,7 +18245,7 @@
       </c>
       <c r="J287" s="3" t="inlineStr"/>
       <c r="K287" s="3" t="inlineStr"/>
-      <c r="L287" s="9" t="inlineStr">
+      <c r="L287" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -18281,9 +18290,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G288" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/jamesclear</t>
+      <c r="G288" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jamesclear</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
@@ -18298,7 +18307,7 @@
       </c>
       <c r="J288" s="3" t="inlineStr"/>
       <c r="K288" s="3" t="inlineStr"/>
-      <c r="L288" s="9" t="inlineStr">
+      <c r="L288" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -18343,9 +18352,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G289" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/nilofer</t>
+      <c r="G289" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nilofer</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr">
@@ -18360,7 +18369,7 @@
       </c>
       <c r="J289" s="3" t="inlineStr"/>
       <c r="K289" s="3" t="inlineStr"/>
-      <c r="L289" s="9" t="inlineStr">
+      <c r="L289" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -18405,9 +18414,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G290" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/nassimtaleb</t>
+      <c r="G290" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nassimtaleb</t>
         </is>
       </c>
       <c r="H290" s="2" t="inlineStr">
@@ -18422,7 +18431,7 @@
       </c>
       <c r="J290" s="3" t="inlineStr"/>
       <c r="K290" s="3" t="inlineStr"/>
-      <c r="L290" s="9" t="inlineStr">
+      <c r="L290" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -18467,9 +18476,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G291" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/dickiebush</t>
+      <c r="G291" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dickiebush</t>
         </is>
       </c>
       <c r="H291" s="2" t="inlineStr">
@@ -18484,7 +18493,7 @@
       </c>
       <c r="J291" s="3" t="inlineStr"/>
       <c r="K291" s="3" t="inlineStr"/>
-      <c r="L291" s="9" t="inlineStr">
+      <c r="L291" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -18529,9 +18538,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G292" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/nicolascole</t>
+      <c r="G292" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nicolascole</t>
         </is>
       </c>
       <c r="H292" s="2" t="inlineStr">
@@ -18546,7 +18555,7 @@
       </c>
       <c r="J292" s="3" t="inlineStr"/>
       <c r="K292" s="3" t="inlineStr"/>
-      <c r="L292" s="9" t="inlineStr">
+      <c r="L292" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -18591,9 +18600,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G293" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/simonsinek</t>
+      <c r="G293" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/simonsinek</t>
         </is>
       </c>
       <c r="H293" s="2" t="inlineStr">
@@ -18608,7 +18617,7 @@
       </c>
       <c r="J293" s="3" t="inlineStr"/>
       <c r="K293" s="3" t="inlineStr"/>
-      <c r="L293" s="9" t="inlineStr">
+      <c r="L293" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -18653,9 +18662,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G294" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/dereksivers</t>
+      <c r="G294" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dereksivers</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr">
@@ -18670,7 +18679,7 @@
       </c>
       <c r="J294" s="3" t="inlineStr"/>
       <c r="K294" s="3" t="inlineStr"/>
-      <c r="L294" s="9" t="inlineStr">
+      <c r="L294" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -18715,9 +18724,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G295" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/ezrafirestone</t>
+      <c r="G295" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ezrafirestone</t>
         </is>
       </c>
       <c r="H295" s="2" t="inlineStr">
@@ -18732,7 +18741,7 @@
       </c>
       <c r="J295" s="3" t="inlineStr"/>
       <c r="K295" s="3" t="inlineStr"/>
-      <c r="L295" s="9" t="inlineStr">
+      <c r="L295" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -18777,9 +18786,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G296" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/chamath</t>
+      <c r="G296" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/chamath</t>
         </is>
       </c>
       <c r="H296" s="2" t="inlineStr">
@@ -18794,7 +18803,7 @@
       </c>
       <c r="J296" s="3" t="inlineStr"/>
       <c r="K296" s="3" t="inlineStr"/>
-      <c r="L296" s="9" t="inlineStr">
+      <c r="L296" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -18839,9 +18848,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G297" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/chrisrawlings</t>
+      <c r="G297" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/chrisrawlings</t>
         </is>
       </c>
       <c r="H297" s="2" t="inlineStr">
@@ -18856,7 +18865,7 @@
       </c>
       <c r="J297" s="3" t="inlineStr"/>
       <c r="K297" s="3" t="inlineStr"/>
-      <c r="L297" s="9" t="inlineStr">
+      <c r="L297" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -18901,9 +18910,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G298" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/sarablakely</t>
+      <c r="G298" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sarablakely</t>
         </is>
       </c>
       <c r="H298" s="2" t="inlineStr">
@@ -18918,7 +18927,7 @@
       </c>
       <c r="J298" s="3" t="inlineStr"/>
       <c r="K298" s="3" t="inlineStr"/>
-      <c r="L298" s="9" t="inlineStr">
+      <c r="L298" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -18963,9 +18972,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G299" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/randfishkin</t>
+      <c r="G299" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/randfishkin</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
@@ -18980,7 +18989,7 @@
       </c>
       <c r="J299" s="3" t="inlineStr"/>
       <c r="K299" s="3" t="inlineStr"/>
-      <c r="L299" s="9" t="inlineStr">
+      <c r="L299" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -19025,9 +19034,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G300" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/sahilbloom</t>
+      <c r="G300" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sahilbloom</t>
         </is>
       </c>
       <c r="H300" s="2" t="inlineStr">
@@ -19042,7 +19051,7 @@
       </c>
       <c r="J300" s="3" t="inlineStr"/>
       <c r="K300" s="3" t="inlineStr"/>
-      <c r="L300" s="9" t="inlineStr">
+      <c r="L300" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -19087,9 +19096,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G301" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/nickshackelford</t>
+      <c r="G301" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nickshackelford</t>
         </is>
       </c>
       <c r="H301" s="2" t="inlineStr">
@@ -19104,7 +19113,7 @@
       </c>
       <c r="J301" s="3" t="inlineStr"/>
       <c r="K301" s="3" t="inlineStr"/>
-      <c r="L301" s="9" t="inlineStr">
+      <c r="L301" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -19149,9 +19158,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G302" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/alanweiss</t>
+      <c r="G302" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alanweiss</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
@@ -19166,7 +19175,7 @@
       </c>
       <c r="J302" s="3" t="inlineStr"/>
       <c r="K302" s="3" t="inlineStr"/>
-      <c r="L302" s="9" t="inlineStr">
+      <c r="L302" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -19211,9 +19220,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G303" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/tomszaky</t>
+      <c r="G303" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tomszaky</t>
         </is>
       </c>
       <c r="H303" s="2" t="inlineStr">
@@ -19228,7 +19237,7 @@
       </c>
       <c r="J303" s="3" t="inlineStr"/>
       <c r="K303" s="3" t="inlineStr"/>
-      <c r="L303" s="9" t="inlineStr">
+      <c r="L303" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -19273,9 +19282,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G304" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/louadler</t>
+      <c r="G304" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/louadler</t>
         </is>
       </c>
       <c r="H304" s="2" t="inlineStr">
@@ -19290,7 +19299,7 @@
       </c>
       <c r="J304" s="3" t="inlineStr"/>
       <c r="K304" s="3" t="inlineStr"/>
-      <c r="L304" s="9" t="inlineStr">
+      <c r="L304" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -19335,9 +19344,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G305" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/robert-rose</t>
+      <c r="G305" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/robert-rose</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
@@ -19352,7 +19361,7 @@
       </c>
       <c r="J305" s="3" t="inlineStr"/>
       <c r="K305" s="3" t="inlineStr"/>
-      <c r="L305" s="9" t="inlineStr">
+      <c r="L305" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -19397,9 +19406,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G306" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/emilyleach</t>
+      <c r="G306" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/emilyleach</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr">
@@ -19414,7 +19423,7 @@
       </c>
       <c r="J306" s="3" t="inlineStr"/>
       <c r="K306" s="3" t="inlineStr"/>
-      <c r="L306" s="9" t="inlineStr">
+      <c r="L306" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -19459,9 +19468,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G307" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/thechrisdo</t>
+      <c r="G307" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/thechrisdo</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -19476,7 +19485,7 @@
       </c>
       <c r="J307" s="3" t="inlineStr"/>
       <c r="K307" s="3" t="inlineStr"/>
-      <c r="L307" s="9" t="inlineStr">
+      <c r="L307" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -19521,9 +19530,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G308" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/daniel-murray-marketing</t>
+      <c r="G308" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/daniel-murray-marketing</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -19538,7 +19547,7 @@
       </c>
       <c r="J308" s="3" t="inlineStr"/>
       <c r="K308" s="3" t="inlineStr"/>
-      <c r="L308" s="9" t="inlineStr">
+      <c r="L308" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -19583,9 +19592,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G309" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/justinwelsh</t>
+      <c r="G309" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/justinwelsh</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -19600,7 +19609,7 @@
       </c>
       <c r="J309" s="3" t="inlineStr"/>
       <c r="K309" s="3" t="inlineStr"/>
-      <c r="L309" s="9" t="inlineStr">
+      <c r="L309" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -19645,9 +19654,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G310" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/patricklencioni</t>
+      <c r="G310" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/patricklencioni</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -19662,7 +19671,7 @@
       </c>
       <c r="J310" s="3" t="inlineStr"/>
       <c r="K310" s="3" t="inlineStr"/>
-      <c r="L310" s="9" t="inlineStr">
+      <c r="L310" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -19707,9 +19716,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G311" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/ariannahuffington</t>
+      <c r="G311" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ariannahuffington</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr">
@@ -19724,7 +19733,7 @@
       </c>
       <c r="J311" s="3" t="inlineStr"/>
       <c r="K311" s="3" t="inlineStr"/>
-      <c r="L311" s="9" t="inlineStr">
+      <c r="L311" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -19769,9 +19778,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G312" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/tompeters</t>
+      <c r="G312" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tompeters</t>
         </is>
       </c>
       <c r="H312" s="2" t="inlineStr">
@@ -19786,7 +19795,7 @@
       </c>
       <c r="J312" s="3" t="inlineStr"/>
       <c r="K312" s="3" t="inlineStr"/>
-      <c r="L312" s="9" t="inlineStr">
+      <c r="L312" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -19831,9 +19840,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G313" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/fredwilson</t>
+      <c r="G313" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fredwilson</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -19848,7 +19857,7 @@
       </c>
       <c r="J313" s="3" t="inlineStr"/>
       <c r="K313" s="3" t="inlineStr"/>
-      <c r="L313" s="9" t="inlineStr">
+      <c r="L313" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -19893,9 +19902,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G314" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/ryancraig</t>
+      <c r="G314" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ryancraig</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -19910,7 +19919,7 @@
       </c>
       <c r="J314" s="3" t="inlineStr"/>
       <c r="K314" s="3" t="inlineStr"/>
-      <c r="L314" s="9" t="inlineStr">
+      <c r="L314" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -19955,9 +19964,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G315" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/marksuster</t>
+      <c r="G315" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/marksuster</t>
         </is>
       </c>
       <c r="H315" s="2" t="inlineStr">
@@ -19972,7 +19981,7 @@
       </c>
       <c r="J315" s="3" t="inlineStr"/>
       <c r="K315" s="3" t="inlineStr"/>
-      <c r="L315" s="9" t="inlineStr">
+      <c r="L315" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -20017,9 +20026,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G316" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/garyvaynerchuk</t>
+      <c r="G316" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/garyvaynerchuk</t>
         </is>
       </c>
       <c r="H316" s="2" t="inlineStr">
@@ -20034,7 +20043,7 @@
       </c>
       <c r="J316" s="3" t="inlineStr"/>
       <c r="K316" s="3" t="inlineStr"/>
-      <c r="L316" s="9" t="inlineStr">
+      <c r="L316" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -20079,9 +20088,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G317" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/nataliecofield</t>
+      <c r="G317" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nataliecofield</t>
         </is>
       </c>
       <c r="H317" s="2" t="inlineStr">
@@ -20096,7 +20105,7 @@
       </c>
       <c r="J317" s="3" t="inlineStr"/>
       <c r="K317" s="3" t="inlineStr"/>
-      <c r="L317" s="9" t="inlineStr">
+      <c r="L317" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -20141,9 +20150,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G318" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/adammgrant</t>
+      <c r="G318" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/adammgrant</t>
         </is>
       </c>
       <c r="H318" s="2" t="inlineStr">
@@ -20158,7 +20167,7 @@
       </c>
       <c r="J318" s="3" t="inlineStr"/>
       <c r="K318" s="3" t="inlineStr"/>
-      <c r="L318" s="9" t="inlineStr">
+      <c r="L318" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -20203,9 +20212,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G319" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/andrewwinston</t>
+      <c r="G319" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/andrewwinston</t>
         </is>
       </c>
       <c r="H319" s="2" t="inlineStr">
@@ -20220,7 +20229,7 @@
       </c>
       <c r="J319" s="3" t="inlineStr"/>
       <c r="K319" s="3" t="inlineStr"/>
-      <c r="L319" s="9" t="inlineStr">
+      <c r="L319" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -20265,9 +20274,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G320" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/lizwiseman</t>
+      <c r="G320" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lizwiseman</t>
         </is>
       </c>
       <c r="H320" s="2" t="inlineStr">
@@ -20282,7 +20291,7 @@
       </c>
       <c r="J320" s="3" t="inlineStr"/>
       <c r="K320" s="3" t="inlineStr"/>
-      <c r="L320" s="9" t="inlineStr">
+      <c r="L320" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -20327,9 +20336,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G321" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/vickirobin</t>
+      <c r="G321" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vickirobin</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -20344,7 +20353,7 @@
       </c>
       <c r="J321" s="3" t="inlineStr"/>
       <c r="K321" s="3" t="inlineStr"/>
-      <c r="L321" s="9" t="inlineStr">
+      <c r="L321" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -20389,9 +20398,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G322" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/zdoggmd</t>
+      <c r="G322" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/zdoggmd</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -20406,7 +20415,7 @@
       </c>
       <c r="J322" s="3" t="inlineStr"/>
       <c r="K322" s="3" t="inlineStr"/>
-      <c r="L322" s="9" t="inlineStr">
+      <c r="L322" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -20451,9 +20460,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G323" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/shamahyder</t>
+      <c r="G323" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/shamahyder</t>
         </is>
       </c>
       <c r="H323" s="2" t="inlineStr">
@@ -20468,7 +20477,7 @@
       </c>
       <c r="J323" s="3" t="inlineStr"/>
       <c r="K323" s="3" t="inlineStr"/>
-      <c r="L323" s="9" t="inlineStr">
+      <c r="L323" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -20513,9 +20522,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G324" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/aayushbhatnagar</t>
+      <c r="G324" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/aayushbhatnagar</t>
         </is>
       </c>
       <c r="H324" s="2" t="inlineStr">
@@ -20530,7 +20539,7 @@
       </c>
       <c r="J324" s="3" t="inlineStr"/>
       <c r="K324" s="3" t="inlineStr"/>
-      <c r="L324" s="8" t="inlineStr">
+      <c r="L324" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -20575,9 +20584,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G325" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/tariqalqahtani</t>
+      <c r="G325" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tariqalqahtani</t>
         </is>
       </c>
       <c r="H325" s="2" t="inlineStr">
@@ -20592,7 +20601,7 @@
       </c>
       <c r="J325" s="3" t="inlineStr"/>
       <c r="K325" s="3" t="inlineStr"/>
-      <c r="L325" s="8" t="inlineStr">
+      <c r="L325" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -20637,9 +20646,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G326" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/sunilmittal</t>
+      <c r="G326" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sunilmittal</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -20654,7 +20663,7 @@
       </c>
       <c r="J326" s="3" t="inlineStr"/>
       <c r="K326" s="3" t="inlineStr"/>
-      <c r="L326" s="9" t="inlineStr">
+      <c r="L326" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -20699,9 +20708,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G327" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/fawazalhokair</t>
+      <c r="G327" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fawazalhokair</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">
@@ -20716,7 +20725,7 @@
       </c>
       <c r="J327" s="3" t="inlineStr"/>
       <c r="K327" s="3" t="inlineStr"/>
-      <c r="L327" s="9" t="inlineStr">
+      <c r="L327" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -20761,9 +20770,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G328" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/sarmadziok</t>
+      <c r="G328" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sarmadziok</t>
         </is>
       </c>
       <c r="H328" s="2" t="inlineStr">
@@ -20778,7 +20787,7 @@
       </c>
       <c r="J328" s="3" t="inlineStr"/>
       <c r="K328" s="3" t="inlineStr"/>
-      <c r="L328" s="9" t="inlineStr">
+      <c r="L328" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -20823,9 +20832,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G329" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/aidangomez</t>
+      <c r="G329" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/aidangomez</t>
         </is>
       </c>
       <c r="H329" s="2" t="inlineStr">
@@ -20840,7 +20849,7 @@
       </c>
       <c r="J329" s="3" t="inlineStr"/>
       <c r="K329" s="3" t="inlineStr"/>
-      <c r="L329" s="9" t="inlineStr">
+      <c r="L329" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -20885,9 +20894,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G330" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/katelynbourgoin</t>
+      <c r="G330" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/katelynbourgoin</t>
         </is>
       </c>
       <c r="H330" s="2" t="inlineStr">
@@ -20902,7 +20911,7 @@
       </c>
       <c r="J330" s="3" t="inlineStr"/>
       <c r="K330" s="3" t="inlineStr"/>
-      <c r="L330" s="9" t="inlineStr">
+      <c r="L330" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -20947,9 +20956,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G331" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/sureshvaswani</t>
+      <c r="G331" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sureshvaswani</t>
         </is>
       </c>
       <c r="H331" s="2" t="inlineStr">
@@ -20964,7 +20973,7 @@
       </c>
       <c r="J331" s="3" t="inlineStr"/>
       <c r="K331" s="3" t="inlineStr"/>
-      <c r="L331" s="9" t="inlineStr">
+      <c r="L331" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -21009,9 +21018,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G332" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/adriangore</t>
+      <c r="G332" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/adriangore</t>
         </is>
       </c>
       <c r="H332" s="2" t="inlineStr">
@@ -21026,7 +21035,7 @@
       </c>
       <c r="J332" s="3" t="inlineStr"/>
       <c r="K332" s="3" t="inlineStr"/>
-      <c r="L332" s="9" t="inlineStr">
+      <c r="L332" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -21071,9 +21080,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G333" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/shaymenuchin</t>
+      <c r="G333" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/shaymenuchin</t>
         </is>
       </c>
       <c r="H333" s="2" t="inlineStr">
@@ -21088,7 +21097,7 @@
       </c>
       <c r="J333" s="3" t="inlineStr"/>
       <c r="K333" s="3" t="inlineStr"/>
-      <c r="L333" s="9" t="inlineStr">
+      <c r="L333" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -21133,9 +21142,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G334" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/paragkhanna</t>
+      <c r="G334" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/paragkhanna</t>
         </is>
       </c>
       <c r="H334" s="2" t="inlineStr">
@@ -21150,7 +21159,7 @@
       </c>
       <c r="J334" s="3" t="inlineStr"/>
       <c r="K334" s="3" t="inlineStr"/>
-      <c r="L334" s="9" t="inlineStr">
+      <c r="L334" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -21195,9 +21204,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G335" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/yvonneike</t>
+      <c r="G335" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/yvonneike</t>
         </is>
       </c>
       <c r="H335" s="2" t="inlineStr">
@@ -21212,7 +21221,7 @@
       </c>
       <c r="J335" s="3" t="inlineStr"/>
       <c r="K335" s="3" t="inlineStr"/>
-      <c r="L335" s="9" t="inlineStr">
+      <c r="L335" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -21257,9 +21266,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G336" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/michellejraymond</t>
+      <c r="G336" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/michellejraymond</t>
         </is>
       </c>
       <c r="H336" s="2" t="inlineStr">
@@ -21274,7 +21283,7 @@
       </c>
       <c r="J336" s="3" t="inlineStr"/>
       <c r="K336" s="3" t="inlineStr"/>
-      <c r="L336" s="9" t="inlineStr">
+      <c r="L336" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -21319,9 +21328,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G337" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/colmlauder</t>
+      <c r="G337" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/colmlauder</t>
         </is>
       </c>
       <c r="H337" s="2" t="inlineStr">
@@ -21336,7 +21345,7 @@
       </c>
       <c r="J337" s="3" t="inlineStr"/>
       <c r="K337" s="3" t="inlineStr"/>
-      <c r="L337" s="9" t="inlineStr">
+      <c r="L337" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -21381,9 +21390,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G338" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/ginacleo</t>
+      <c r="G338" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ginacleo</t>
         </is>
       </c>
       <c r="H338" s="2" t="inlineStr">
@@ -21398,7 +21407,7 @@
       </c>
       <c r="J338" s="3" t="inlineStr"/>
       <c r="K338" s="3" t="inlineStr"/>
-      <c r="L338" s="9" t="inlineStr">
+      <c r="L338" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -21443,9 +21452,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G339" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/grettavanriel</t>
+      <c r="G339" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/grettavanriel</t>
         </is>
       </c>
       <c r="H339" s="2" t="inlineStr">
@@ -21460,7 +21469,7 @@
       </c>
       <c r="J339" s="3" t="inlineStr"/>
       <c r="K339" s="3" t="inlineStr"/>
-      <c r="L339" s="9" t="inlineStr">
+      <c r="L339" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -21505,9 +21514,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G340" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/paulpolman</t>
+      <c r="G340" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/paulpolman</t>
         </is>
       </c>
       <c r="H340" s="2" t="inlineStr">
@@ -21522,7 +21531,7 @@
       </c>
       <c r="J340" s="3" t="inlineStr"/>
       <c r="K340" s="3" t="inlineStr"/>
-      <c r="L340" s="9" t="inlineStr">
+      <c r="L340" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -21567,9 +21576,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G341" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/gadkari-nitin</t>
+      <c r="G341" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/gadkari-nitin</t>
         </is>
       </c>
       <c r="H341" s="2" t="inlineStr">
@@ -21584,7 +21593,7 @@
       </c>
       <c r="J341" s="3" t="inlineStr"/>
       <c r="K341" s="3" t="inlineStr"/>
-      <c r="L341" s="9" t="inlineStr">
+      <c r="L341" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -21629,9 +21638,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G342" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/pradeep-chauhan</t>
+      <c r="G342" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/pradeep-chauhan</t>
         </is>
       </c>
       <c r="H342" s="2" t="inlineStr">
@@ -21646,7 +21655,7 @@
       </c>
       <c r="J342" s="3" t="inlineStr"/>
       <c r="K342" s="3" t="inlineStr"/>
-      <c r="L342" s="9" t="inlineStr">
+      <c r="L342" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -21691,9 +21700,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G343" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/vikramsinha</t>
+      <c r="G343" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vikramsinha</t>
         </is>
       </c>
       <c r="H343" s="2" t="inlineStr">
@@ -21708,7 +21717,7 @@
       </c>
       <c r="J343" s="3" t="inlineStr"/>
       <c r="K343" s="3" t="inlineStr"/>
-      <c r="L343" s="9" t="inlineStr">
+      <c r="L343" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -21753,9 +21762,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G344" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/arthurfogel</t>
+      <c r="G344" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/arthurfogel</t>
         </is>
       </c>
       <c r="H344" s="2" t="inlineStr">
@@ -21770,7 +21779,7 @@
       </c>
       <c r="J344" s="3" t="inlineStr"/>
       <c r="K344" s="3" t="inlineStr"/>
-      <c r="L344" s="9" t="inlineStr">
+      <c r="L344" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -21815,9 +21824,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G345" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/thomasseale</t>
+      <c r="G345" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/thomasseale</t>
         </is>
       </c>
       <c r="H345" s="2" t="inlineStr">
@@ -21832,7 +21841,7 @@
       </c>
       <c r="J345" s="3" t="inlineStr"/>
       <c r="K345" s="3" t="inlineStr"/>
-      <c r="L345" s="9" t="inlineStr">
+      <c r="L345" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -21877,9 +21886,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G346" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/bertalanmesko</t>
+      <c r="G346" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/bertalanmesko</t>
         </is>
       </c>
       <c r="H346" s="2" t="inlineStr">
@@ -21894,7 +21903,7 @@
       </c>
       <c r="J346" s="3" t="inlineStr"/>
       <c r="K346" s="3" t="inlineStr"/>
-      <c r="L346" s="9" t="inlineStr">
+      <c r="L346" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -21939,9 +21948,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G347" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/amandahoffmann</t>
+      <c r="G347" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/amandahoffmann</t>
         </is>
       </c>
       <c r="H347" s="2" t="inlineStr">
@@ -21956,7 +21965,7 @@
       </c>
       <c r="J347" s="3" t="inlineStr"/>
       <c r="K347" s="3" t="inlineStr"/>
-      <c r="L347" s="9" t="inlineStr">
+      <c r="L347" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -22001,9 +22010,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G348" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/pieterdlvng</t>
+      <c r="G348" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/pieterdlvng</t>
         </is>
       </c>
       <c r="H348" s="2" t="inlineStr">
@@ -22018,7 +22027,7 @@
       </c>
       <c r="J348" s="3" t="inlineStr"/>
       <c r="K348" s="3" t="inlineStr"/>
-      <c r="L348" s="9" t="inlineStr">
+      <c r="L348" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -22063,9 +22072,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G349" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/omarsysavane</t>
+      <c r="G349" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/omarsysavane</t>
         </is>
       </c>
       <c r="H349" s="2" t="inlineStr">
@@ -22080,7 +22089,7 @@
       </c>
       <c r="J349" s="3" t="inlineStr"/>
       <c r="K349" s="3" t="inlineStr"/>
-      <c r="L349" s="9" t="inlineStr">
+      <c r="L349" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -22125,9 +22134,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G350" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/naguibsawiris</t>
+      <c r="G350" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/naguibsawiris</t>
         </is>
       </c>
       <c r="H350" s="2" t="inlineStr">
@@ -22142,7 +22151,7 @@
       </c>
       <c r="J350" s="3" t="inlineStr"/>
       <c r="K350" s="3" t="inlineStr"/>
-      <c r="L350" s="9" t="inlineStr">
+      <c r="L350" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -22187,9 +22196,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G351" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/siddharthrao</t>
+      <c r="G351" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/siddharthrao</t>
         </is>
       </c>
       <c r="H351" s="2" t="inlineStr">
@@ -22204,7 +22213,7 @@
       </c>
       <c r="J351" s="3" t="inlineStr"/>
       <c r="K351" s="3" t="inlineStr"/>
-      <c r="L351" s="9" t="inlineStr">
+      <c r="L351" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -22249,9 +22258,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G352" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/petrafisher</t>
+      <c r="G352" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/petrafisher</t>
         </is>
       </c>
       <c r="H352" s="2" t="inlineStr">
@@ -22266,7 +22275,7 @@
       </c>
       <c r="J352" s="3" t="inlineStr"/>
       <c r="K352" s="3" t="inlineStr"/>
-      <c r="L352" s="9" t="inlineStr">
+      <c r="L352" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -22311,9 +22320,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G353" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/roger-martin</t>
+      <c r="G353" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/roger-martin</t>
         </is>
       </c>
       <c r="H353" s="2" t="inlineStr">
@@ -22328,7 +22337,7 @@
       </c>
       <c r="J353" s="3" t="inlineStr"/>
       <c r="K353" s="3" t="inlineStr"/>
-      <c r="L353" s="9" t="inlineStr">
+      <c r="L353" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -22373,9 +22382,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G354" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/aminnasser</t>
+      <c r="G354" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/aminnasser</t>
         </is>
       </c>
       <c r="H354" s="2" t="inlineStr">
@@ -22390,7 +22399,7 @@
       </c>
       <c r="J354" s="3" t="inlineStr"/>
       <c r="K354" s="3" t="inlineStr"/>
-      <c r="L354" s="9" t="inlineStr">
+      <c r="L354" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -22435,9 +22444,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G355" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/aamir-khan-investor</t>
+      <c r="G355" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/aamir-khan-investor</t>
         </is>
       </c>
       <c r="H355" s="2" t="inlineStr">
@@ -22452,7 +22461,7 @@
       </c>
       <c r="J355" s="3" t="inlineStr"/>
       <c r="K355" s="3" t="inlineStr"/>
-      <c r="L355" s="9" t="inlineStr">
+      <c r="L355" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -22497,9 +22506,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G356" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/jasmin-alic</t>
+      <c r="G356" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jasmin-alic</t>
         </is>
       </c>
       <c r="H356" s="2" t="inlineStr">
@@ -22514,7 +22523,7 @@
       </c>
       <c r="J356" s="3" t="inlineStr"/>
       <c r="K356" s="3" t="inlineStr"/>
-      <c r="L356" s="9" t="inlineStr">
+      <c r="L356" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -22559,9 +22568,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G357" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/rajananandan</t>
+      <c r="G357" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rajananandan</t>
         </is>
       </c>
       <c r="H357" s="2" t="inlineStr">
@@ -22576,7 +22585,7 @@
       </c>
       <c r="J357" s="3" t="inlineStr"/>
       <c r="K357" s="3" t="inlineStr"/>
-      <c r="L357" s="9" t="inlineStr">
+      <c r="L357" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -22621,9 +22630,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G358" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/harleyfinkelstein</t>
+      <c r="G358" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/harleyfinkelstein</t>
         </is>
       </c>
       <c r="H358" s="2" t="inlineStr">
@@ -22638,7 +22647,7 @@
       </c>
       <c r="J358" s="3" t="inlineStr"/>
       <c r="K358" s="3" t="inlineStr"/>
-      <c r="L358" s="9" t="inlineStr">
+      <c r="L358" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -22683,9 +22692,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G359" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/masayoshi-son</t>
+      <c r="G359" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/masayoshi-son</t>
         </is>
       </c>
       <c r="H359" s="2" t="inlineStr">
@@ -22700,7 +22709,7 @@
       </c>
       <c r="J359" s="3" t="inlineStr"/>
       <c r="K359" s="3" t="inlineStr"/>
-      <c r="L359" s="9" t="inlineStr">
+      <c r="L359" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -22745,9 +22754,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G360" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/bertrand-piccard</t>
+      <c r="G360" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/bertrand-piccard</t>
         </is>
       </c>
       <c r="H360" s="2" t="inlineStr">
@@ -22762,7 +22771,7 @@
       </c>
       <c r="J360" s="3" t="inlineStr"/>
       <c r="K360" s="3" t="inlineStr"/>
-      <c r="L360" s="9" t="inlineStr">
+      <c r="L360" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -22807,9 +22816,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G361" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/leahbjornson</t>
+      <c r="G361" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/leahbjornson</t>
         </is>
       </c>
       <c r="H361" s="2" t="inlineStr">
@@ -22824,7 +22833,7 @@
       </c>
       <c r="J361" s="3" t="inlineStr"/>
       <c r="K361" s="3" t="inlineStr"/>
-      <c r="L361" s="9" t="inlineStr">
+      <c r="L361" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -22869,9 +22878,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G362" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/audreyt</t>
+      <c r="G362" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/audreyt</t>
         </is>
       </c>
       <c r="H362" s="2" t="inlineStr">
@@ -22886,7 +22895,7 @@
       </c>
       <c r="J362" s="3" t="inlineStr"/>
       <c r="K362" s="3" t="inlineStr"/>
-      <c r="L362" s="9" t="inlineStr">
+      <c r="L362" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -22931,9 +22940,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G363" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/priyankasalot</t>
+      <c r="G363" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/priyankasalot</t>
         </is>
       </c>
       <c r="H363" s="2" t="inlineStr">
@@ -22948,7 +22957,7 @@
       </c>
       <c r="J363" s="3" t="inlineStr"/>
       <c r="K363" s="3" t="inlineStr"/>
-      <c r="L363" s="9" t="inlineStr">
+      <c r="L363" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -22993,9 +23002,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G364" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/rogerfederer</t>
+      <c r="G364" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rogerfederer</t>
         </is>
       </c>
       <c r="H364" s="2" t="inlineStr">
@@ -23010,7 +23019,7 @@
       </c>
       <c r="J364" s="3" t="inlineStr"/>
       <c r="K364" s="3" t="inlineStr"/>
-      <c r="L364" s="9" t="inlineStr">
+      <c r="L364" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -23055,9 +23064,9 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G365" s="3" t="inlineStr">
-        <is>
-          <t>linkedin.com/in/nikhilkamath</t>
+      <c r="G365" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nikhilkamath</t>
         </is>
       </c>
       <c r="H365" s="2" t="inlineStr">
@@ -23072,7 +23081,7 @@
       </c>
       <c r="J365" s="3" t="inlineStr"/>
       <c r="K365" s="3" t="inlineStr"/>
-      <c r="L365" s="9" t="inlineStr">
+      <c r="L365" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -23090,6 +23099,348 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:N365"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G96" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G97" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G100" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G104" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G106" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G108" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G112" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G114" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G123" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G125" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G127" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G129" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G130" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G131" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G132" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G133" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G134" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G135" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G137" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G138" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G139" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G140" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G141" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G142" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G143" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G144" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G145" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G147" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G148" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G149" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G150" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G151" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G152" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G153" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G154" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G155" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G156" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G157" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G158" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G159" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G160" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G161" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G162" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G163" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G164" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G165" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G166" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G167" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G168" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G169" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G170" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G171" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G172" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G173" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G174" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G175" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G176" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G177" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G178" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G179" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G180" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G181" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G182" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G183" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G184" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G185" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G186" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G187" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G188" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G189" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G190" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G191" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G192" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G193" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G194" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G195" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G196" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G197" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G198" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G199" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G200" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G201" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G202" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G203" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G204" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G205" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G206" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G207" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G208" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G209" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G210" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G211" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G212" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G213" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G214" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G215" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G216" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G217" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G218" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G219" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G220" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G221" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G222" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G223" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G224" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G225" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G226" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G227" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G228" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G229" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G230" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G231" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G232" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G233" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G234" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G235" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G236" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G237" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G238" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G239" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G240" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G241" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G242" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G243" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G244" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G245" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G246" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G247" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G248" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G249" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G250" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G251" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G252" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G253" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G254" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G255" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G256" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G257" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G258" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G259" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G260" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G261" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G262" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G263" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G264" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G265" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G266" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G267" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G268" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G269" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G270" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G271" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G272" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G273" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G274" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G275" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G276" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G277" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G278" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G279" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G280" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G281" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G282" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G283" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G284" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G285" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G286" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G287" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G288" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G289" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G290" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G291" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G292" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G293" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G294" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G295" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G296" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G297" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G298" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G299" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G300" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G301" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G302" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G303" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G304" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G305" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G306" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G307" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G308" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G309" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G310" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G311" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G312" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G313" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G314" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G315" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G316" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G317" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G318" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G319" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G320" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G321" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G322" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G323" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G324" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G325" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G326" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G327" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G328" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G329" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G330" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G331" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G332" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G333" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G334" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G335" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G336" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G337" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G338" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G339" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G340" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G341" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G342" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G343" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G344" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G345" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G346" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G347" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G348" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G349" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G350" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G351" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G352" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G353" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G354" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G355" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G356" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G357" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G358" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G359" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G360" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G361" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G362" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G363" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G364" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G365" r:id="rId340"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -23144,7 +23495,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>Methodology note</t>
         </is>
@@ -23176,7 +23527,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>Methodology note</t>
         </is>
@@ -23204,7 +23555,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Methodology note</t>
         </is>
@@ -23232,7 +23583,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Methodology note</t>
         </is>
@@ -23260,7 +23611,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Methodology note</t>
         </is>
@@ -23288,7 +23639,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Methodology note</t>
         </is>
@@ -23316,7 +23667,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Methodology note</t>
         </is>
@@ -23344,7 +23695,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Methodology note</t>
         </is>
@@ -23372,7 +23723,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>Conflict resolved</t>
         </is>
@@ -23404,7 +23755,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Conflict resolved</t>
         </is>
@@ -23436,7 +23787,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Conflict resolved</t>
         </is>
@@ -23468,7 +23819,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Conflict resolved</t>
         </is>
@@ -23500,7 +23851,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Conflict resolved</t>
         </is>
@@ -23532,7 +23883,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Conflict resolved</t>
         </is>
@@ -23564,7 +23915,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>Conflict resolved</t>
         </is>
@@ -23596,7 +23947,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>Conflict resolved</t>
         </is>
@@ -23628,7 +23979,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Conflict resolved</t>
         </is>
@@ -23660,7 +24011,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>Conflict resolved</t>
         </is>
@@ -23692,7 +24043,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>Merged duplicate</t>
         </is>
@@ -23724,7 +24075,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>Merged duplicate</t>
         </is>
@@ -23756,7 +24107,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>Merged duplicate</t>
         </is>
@@ -23788,7 +24139,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>Merged duplicate</t>
         </is>
@@ -23820,7 +24171,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>Merged duplicate</t>
         </is>
@@ -23852,7 +24203,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>Merged duplicate</t>
         </is>
@@ -23884,7 +24235,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>Merged duplicate</t>
         </is>
@@ -23916,7 +24267,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>Merged duplicate</t>
         </is>
@@ -23948,7 +24299,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>Merged duplicate</t>
         </is>
@@ -23980,7 +24331,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="inlineStr">
+      <c r="A29" s="13" t="inlineStr">
         <is>
           <t>Merged duplicate</t>
         </is>
@@ -24012,7 +24363,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="inlineStr">
+      <c r="A30" s="13" t="inlineStr">
         <is>
           <t>Merged duplicate</t>
         </is>
@@ -24044,7 +24395,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="inlineStr">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>Merged duplicate</t>
         </is>
@@ -24076,7 +24427,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>Merged duplicate</t>
         </is>
@@ -24108,7 +24459,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="inlineStr">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>Merged duplicate</t>
         </is>
@@ -24140,7 +24491,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="inlineStr">
+      <c r="A34" s="13" t="inlineStr">
         <is>
           <t>Merged duplicate</t>
         </is>
@@ -24172,7 +24523,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="12" t="inlineStr">
+      <c r="A35" s="13" t="inlineStr">
         <is>
           <t>Merged duplicate</t>
         </is>
@@ -24204,7 +24555,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="13" t="inlineStr">
+      <c r="A36" s="14" t="inlineStr">
         <is>
           <t>Needs manual NAME</t>
         </is>
@@ -24232,7 +24583,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="13" t="inlineStr">
+      <c r="A37" s="14" t="inlineStr">
         <is>
           <t>Needs manual NAME</t>
         </is>
@@ -24260,7 +24611,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="13" t="inlineStr">
+      <c r="A38" s="14" t="inlineStr">
         <is>
           <t>Needs manual NAME</t>
         </is>
@@ -24288,7 +24639,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="13" t="inlineStr">
+      <c r="A39" s="14" t="inlineStr">
         <is>
           <t>Needs manual NAME</t>
         </is>
@@ -24316,7 +24667,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="13" t="inlineStr">
+      <c r="A40" s="14" t="inlineStr">
         <is>
           <t>Needs manual NAME</t>
         </is>
@@ -24344,7 +24695,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="13" t="inlineStr">
+      <c r="A41" s="14" t="inlineStr">
         <is>
           <t>Needs manual NAME</t>
         </is>
@@ -24372,7 +24723,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="13" t="inlineStr">
+      <c r="A42" s="14" t="inlineStr">
         <is>
           <t>Needs manual NAME</t>
         </is>
@@ -24400,7 +24751,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="13" t="inlineStr">
+      <c r="A43" s="14" t="inlineStr">
         <is>
           <t>Needs manual NAME</t>
         </is>
@@ -24428,7 +24779,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="13" t="inlineStr">
+      <c r="A44" s="14" t="inlineStr">
         <is>
           <t>Needs manual NAME</t>
         </is>
@@ -24456,7 +24807,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="13" t="inlineStr">
+      <c r="A45" s="14" t="inlineStr">
         <is>
           <t>Needs manual NAME</t>
         </is>
@@ -24484,7 +24835,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="13" t="inlineStr">
+      <c r="A46" s="14" t="inlineStr">
         <is>
           <t>Needs manual NAME</t>
         </is>
@@ -24512,7 +24863,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="13" t="inlineStr">
+      <c r="A47" s="14" t="inlineStr">
         <is>
           <t>Needs manual URL</t>
         </is>
@@ -24540,7 +24891,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="13" t="inlineStr">
+      <c r="A48" s="14" t="inlineStr">
         <is>
           <t>Needs manual URL</t>
         </is>
@@ -24568,7 +24919,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="13" t="inlineStr">
+      <c r="A49" s="14" t="inlineStr">
         <is>
           <t>Needs manual URL</t>
         </is>
@@ -24596,7 +24947,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="13" t="inlineStr">
+      <c r="A50" s="14" t="inlineStr">
         <is>
           <t>Needs manual URL</t>
         </is>
@@ -24624,7 +24975,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="13" t="inlineStr">
+      <c r="A51" s="14" t="inlineStr">
         <is>
           <t>Needs manual URL</t>
         </is>
@@ -24652,7 +25003,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="13" t="inlineStr">
+      <c r="A52" s="14" t="inlineStr">
         <is>
           <t>Needs manual URL</t>
         </is>
@@ -24680,7 +25031,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="13" t="inlineStr">
+      <c r="A53" s="14" t="inlineStr">
         <is>
           <t>Needs manual URL</t>
         </is>
@@ -24708,7 +25059,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="13" t="inlineStr">
+      <c r="A54" s="14" t="inlineStr">
         <is>
           <t>Needs manual URL</t>
         </is>
@@ -24736,7 +25087,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="13" t="inlineStr">
+      <c r="A55" s="14" t="inlineStr">
         <is>
           <t>Needs manual URL</t>
         </is>
@@ -24764,7 +25115,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="13" t="inlineStr">
+      <c r="A56" s="14" t="inlineStr">
         <is>
           <t>Needs manual URL</t>
         </is>
@@ -24792,7 +25143,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="13" t="inlineStr">
+      <c r="A57" s="14" t="inlineStr">
         <is>
           <t>Needs manual URL</t>
         </is>
@@ -24820,7 +25171,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="13" t="inlineStr">
+      <c r="A58" s="14" t="inlineStr">
         <is>
           <t>Needs manual URL</t>
         </is>
@@ -24848,7 +25199,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="13" t="inlineStr">
+      <c r="A59" s="14" t="inlineStr">
         <is>
           <t>Needs manual URL</t>
         </is>
@@ -24876,7 +25227,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="13" t="inlineStr">
+      <c r="A60" s="14" t="inlineStr">
         <is>
           <t>Needs manual URL</t>
         </is>
@@ -24904,7 +25255,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="13" t="inlineStr">
+      <c r="A61" s="14" t="inlineStr">
         <is>
           <t>Needs manual URL</t>
         </is>
@@ -24932,7 +25283,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="13" t="inlineStr">
+      <c r="A62" s="14" t="inlineStr">
         <is>
           <t>Needs manual URL</t>
         </is>
@@ -24960,7 +25311,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="13" t="inlineStr">
+      <c r="A63" s="14" t="inlineStr">
         <is>
           <t>Needs manual URL</t>
         </is>
@@ -24988,7 +25339,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="13" t="inlineStr">
+      <c r="A64" s="14" t="inlineStr">
         <is>
           <t>Needs manual URL</t>
         </is>
@@ -25016,7 +25367,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="13" t="inlineStr">
+      <c r="A65" s="14" t="inlineStr">
         <is>
           <t>Needs manual URL</t>
         </is>
@@ -25044,7 +25395,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="13" t="inlineStr">
+      <c r="A66" s="14" t="inlineStr">
         <is>
           <t>Needs manual URL</t>
         </is>
@@ -25072,7 +25423,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="13" t="inlineStr">
+      <c r="A67" s="14" t="inlineStr">
         <is>
           <t>Needs manual URL</t>
         </is>
@@ -25100,7 +25451,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="13" t="inlineStr">
+      <c r="A68" s="14" t="inlineStr">
         <is>
           <t>Needs manual URL</t>
         </is>
@@ -25128,7 +25479,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="13" t="inlineStr">
+      <c r="A69" s="14" t="inlineStr">
         <is>
           <t>Needs manual URL</t>
         </is>
@@ -25156,7 +25507,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="13" t="inlineStr">
+      <c r="A70" s="14" t="inlineStr">
         <is>
           <t>Needs manual URL</t>
         </is>
